--- a/Claude outputs/Peserta_Pelatihan_Bencana_4Kelas_1-3_6Okt2026.xlsx
+++ b/Claude outputs/Peserta_Pelatihan_Bencana_4Kelas_1-3_6Okt2026.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Perlu Konfirmasi" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Daftar Peserta'!$A$4:$M$92</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Daftar Peserta'!$A$4:$M$96</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="937" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="971" uniqueCount="339">
   <si>
     <t xml:space="preserve">Peserta pelatihan petugas pendataan bencana</t>
   </si>
@@ -128,7 +128,7 @@
     <t xml:space="preserve">2. Pilihan jadwal diambil dari isian petugas (7 Okt / 8 Okt / keduanya). Usulan meminimalkan anggota yang harus pindah dari pilihannya; lihat kolom "Sesuai pilihan?" dan sheet "Perlu Konfirmasi".</t>
   </si>
   <si>
-    <t xml:space="preserve">3. Aturan kelas 20-27 peserta: 79 peserta + 8 sit-in organik (8 Okt) = 87 orang = 4 kelas. Panitia 2 orang per kelas dihitung terpisah.</t>
+    <t xml:space="preserve">3. Aturan kelas 20-27 peserta: 83 peserta + 8 sit-in organik (8 Okt) = 91 orang = 4 kelas. Panitia 2 orang per kelas dihitung terpisah. Devi Kardila, Berni Desriyanti, Marvi Gusneriza, dan Leni Marta ditambahkan atas arahan 6 Okt.</t>
   </si>
   <si>
     <t xml:space="preserve">4. Masih ada ± 60 petugas yang sudah konfirmasi tetapi belum masuk grup WA; belum dihitung di sini.</t>
@@ -413,6 +413,18 @@
     <t xml:space="preserve">+6282171992943</t>
   </si>
   <si>
+    <t xml:space="preserve">Devi Kardila</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+6282285034316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(belum bergabung)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ditambahkan atas arahan; status database masih menolak. Belum bergabung grup WA</t>
+  </si>
+  <si>
     <t xml:space="preserve">Yusnita susanti</t>
   </si>
   <si>
@@ -590,6 +602,15 @@
     <t xml:space="preserve">+6282288879380</t>
   </si>
   <si>
+    <t xml:space="preserve">Berni desriyanti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+6285374078252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ditambahkan atas arahan; sebelumnya menolak, kini bersedia (6 Okt). Belum bergabung grup WA</t>
+  </si>
+  <si>
     <t xml:space="preserve">Megawati</t>
   </si>
   <si>
@@ -764,6 +785,15 @@
     <t xml:space="preserve">+6285274886688</t>
   </si>
   <si>
+    <t xml:space="preserve">Marvi gusneriza</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+6282285119197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ditambahkan 6 Okt (status diterima); peran dan PML belum ditentukan; belum bergabung grup WA</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ardial Jaraf</t>
   </si>
   <si>
@@ -908,6 +938,9 @@
     <t xml:space="preserve">+6285763788768</t>
   </si>
   <si>
+    <t xml:space="preserve">Leni Marta</t>
+  </si>
+  <si>
     <t xml:space="preserve">Mirvan Harvia</t>
   </si>
   <si>
@@ -950,7 +983,7 @@
     <t xml:space="preserve">Mailani Putri + Arini Alva Syaadah</t>
   </si>
   <si>
-    <t xml:space="preserve">Tanpa PML (2); Dessy Meiyarni (2); Hariston (PML organik) (3); Rifa Amelia (PML, menolak) (1); Widya Elvera (4); Widya Verawati (4); Yurneti (4); Yusnita Susanti (4)</t>
+    <t xml:space="preserve">Tanpa PML (2); Dessy Meiyarni (2); Hariston (PML organik) (3); Rifa Amelia (PML, menolak) (1); Widya Elvera (4); Widya Verawati (4); Yurneti (5); Yusnita Susanti (4)</t>
   </si>
   <si>
     <t xml:space="preserve">8 Okt 2026</t>
@@ -959,19 +992,19 @@
     <t xml:space="preserve">Faisal Siddiq + Dina Marizka</t>
   </si>
   <si>
-    <t xml:space="preserve">Ayu Sepriani (2); Budi Pernandes (5); Ferianto (5); Irawita (5); Megawati (2)</t>
+    <t xml:space="preserve">Ayu Sepriani (2); Budi Pernandes (5); Ferianto (5); Irawita (6); Megawati (2)</t>
   </si>
   <si>
     <t xml:space="preserve">Oryza Maria Ulva + Nurafiza Thamrin</t>
   </si>
   <si>
-    <t xml:space="preserve">Lia Angraini (4); Lucky Melan Sari (5); Mega Nana Yulianti (5); Saputra Ebel Feri (4)</t>
+    <t xml:space="preserve">Lia Angraini (4); Lucky Melan Sari (5); Mega Nana Yulianti (5); Saputra Ebel Feri (4); Tanpa PML (1)</t>
   </si>
   <si>
     <t xml:space="preserve">Alex Kandria + Witria Dasni</t>
   </si>
   <si>
-    <t xml:space="preserve">Tanpa PML (1); Ilham (PML organik) (4); Usyenti (6); Yelli Novita Sari (2); Yeni Siswanti (5)</t>
+    <t xml:space="preserve">Tanpa PML (2); Ilham (PML organik) (4); Usyenti (6); Yelli Novita Sari (2); Yeni Siswanti (5)</t>
   </si>
   <si>
     <t xml:space="preserve">Nama panitia pada kolom Panitia adalah USUL (pegawai organik); silakan ganti. Kelas 1 = 7 Okt, kelas 2-4 = 8 Okt.</t>
@@ -1526,8 +1559,8 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="n">
-        <f aca="false">COUNTA('Daftar Peserta'!$B$5:$B$92)</f>
-        <v>88</v>
+        <f aca="false">COUNTA('Daftar Peserta'!$B$5:$B$96)</f>
+        <v>92</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1535,7 +1568,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="n">
-        <f aca="false">COUNTIF('Daftar Peserta'!$C$5:$C$92,"PML")</f>
+        <f aca="false">COUNTIF('Daftar Peserta'!$C$5:$C$96,"PML")</f>
         <v>19</v>
       </c>
     </row>
@@ -1544,8 +1577,8 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="n">
-        <f aca="false">COUNTIF('Daftar Peserta'!$C$5:$C$92,"PPL")</f>
-        <v>60</v>
+        <f aca="false">COUNTIF('Daftar Peserta'!$C$5:$C$96,"PPL")</f>
+        <v>62</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1553,8 +1586,8 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="n">
-        <f aca="false">COUNTIF('Daftar Peserta'!$C$5:$C$92,"-")</f>
-        <v>1</v>
+        <f aca="false">COUNTIF('Daftar Peserta'!$C$5:$C$96,"-")</f>
+        <v>3</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1562,7 +1595,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="n">
-        <f aca="false">COUNTIF('Daftar Peserta'!$M$5:$M$92,"Pegawai organik; di luar*")</f>
+        <f aca="false">COUNTIF('Daftar Peserta'!$M$5:$M$96,"Pegawai organik; di luar*")</f>
         <v>2</v>
       </c>
     </row>
@@ -1571,8 +1604,8 @@
         <v>9</v>
       </c>
       <c r="B10" s="6" t="n">
-        <f aca="false">COUNT('Daftar Peserta'!$K$5:$K$92)</f>
-        <v>87</v>
+        <f aca="false">COUNT('Daftar Peserta'!$K$5:$K$96)</f>
+        <v>91</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1580,7 +1613,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="6" t="n">
-        <f aca="false">COUNTIF('Daftar Peserta'!$C$5:$C$92,"SIT-IN")</f>
+        <f aca="false">COUNTIF('Daftar Peserta'!$C$5:$C$96,"SIT-IN")</f>
         <v>8</v>
       </c>
     </row>
@@ -1589,8 +1622,8 @@
         <v>11</v>
       </c>
       <c r="B12" s="6" t="n">
-        <f aca="false">COUNTIF('Daftar Peserta'!$K$5:$K$92,1)</f>
-        <v>24</v>
+        <f aca="false">COUNTIF('Daftar Peserta'!$K$5:$K$96,1)</f>
+        <v>25</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1598,8 +1631,8 @@
         <v>12</v>
       </c>
       <c r="B13" s="6" t="n">
-        <f aca="false">COUNTIF('Daftar Peserta'!$K$5:$K$92,2)</f>
-        <v>21</v>
+        <f aca="false">COUNTIF('Daftar Peserta'!$K$5:$K$96,2)</f>
+        <v>22</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1607,8 +1640,8 @@
         <v>13</v>
       </c>
       <c r="B14" s="6" t="n">
-        <f aca="false">COUNTIF('Daftar Peserta'!$K$5:$K$92,3)</f>
-        <v>21</v>
+        <f aca="false">COUNTIF('Daftar Peserta'!$K$5:$K$96,3)</f>
+        <v>22</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1616,8 +1649,8 @@
         <v>14</v>
       </c>
       <c r="B15" s="6" t="n">
-        <f aca="false">COUNTIF('Daftar Peserta'!$K$5:$K$92,4)</f>
-        <v>21</v>
+        <f aca="false">COUNTIF('Daftar Peserta'!$K$5:$K$96,4)</f>
+        <v>22</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1633,7 +1666,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="6" t="n">
-        <f aca="false">COUNTIF('Daftar Peserta'!$L$5:$L$92,"Tidak")</f>
+        <f aca="false">COUNTIF('Daftar Peserta'!$L$5:$L$96,"Tidak")</f>
         <v>16</v>
       </c>
     </row>
@@ -1642,7 +1675,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="6" t="n">
-        <f aca="false">COUNTIF('Daftar Peserta'!$H$5:$H$92,"7 Okt")</f>
+        <f aca="false">COUNTIF('Daftar Peserta'!$H$5:$H$96,"7 Okt")</f>
         <v>28</v>
       </c>
     </row>
@@ -1651,7 +1684,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="6" t="n">
-        <f aca="false">COUNTIF('Daftar Peserta'!$H$5:$H$92,"8 Okt")</f>
+        <f aca="false">COUNTIF('Daftar Peserta'!$H$5:$H$96,"8 Okt")</f>
         <v>35</v>
       </c>
     </row>
@@ -1660,7 +1693,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="6" t="n">
-        <f aca="false">COUNTIF('Daftar Peserta'!$H$5:$H$92,"7 &amp; 8 Okt")</f>
+        <f aca="false">COUNTIF('Daftar Peserta'!$H$5:$H$96,"7 &amp; 8 Okt")</f>
         <v>15</v>
       </c>
     </row>
@@ -1677,8 +1710,8 @@
         <v>21</v>
       </c>
       <c r="B23" s="6" t="n">
-        <f aca="false">COUNTIF('Daftar Peserta'!$D$5:$D$92,A23)</f>
-        <v>22</v>
+        <f aca="false">COUNTIF('Daftar Peserta'!$D$5:$D$96,A23)</f>
+        <v>23</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1686,7 +1719,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="6" t="n">
-        <f aca="false">COUNTIF('Daftar Peserta'!$D$5:$D$92,A24)</f>
+        <f aca="false">COUNTIF('Daftar Peserta'!$D$5:$D$96,A24)</f>
         <v>2</v>
       </c>
     </row>
@@ -1695,7 +1728,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="6" t="n">
-        <f aca="false">COUNTIF('Daftar Peserta'!$D$5:$D$92,A25)</f>
+        <f aca="false">COUNTIF('Daftar Peserta'!$D$5:$D$96,A25)</f>
         <v>11</v>
       </c>
     </row>
@@ -1704,8 +1737,8 @@
         <v>24</v>
       </c>
       <c r="B26" s="6" t="n">
-        <f aca="false">COUNTIF('Daftar Peserta'!$D$5:$D$92,A26)</f>
-        <v>30</v>
+        <f aca="false">COUNTIF('Daftar Peserta'!$D$5:$D$96,A26)</f>
+        <v>33</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1713,7 +1746,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="6" t="n">
-        <f aca="false">COUNTIF('Daftar Peserta'!$D$5:$D$92,A27)</f>
+        <f aca="false">COUNTIF('Daftar Peserta'!$D$5:$D$96,A27)</f>
         <v>3</v>
       </c>
     </row>
@@ -1722,7 +1755,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="6" t="n">
-        <f aca="false">COUNTIF('Daftar Peserta'!$D$5:$D$92,A28)</f>
+        <f aca="false">COUNTIF('Daftar Peserta'!$D$5:$D$96,A28)</f>
         <v>1</v>
       </c>
     </row>
@@ -1731,7 +1764,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="6" t="n">
-        <f aca="false">COUNTIF('Daftar Peserta'!$D$5:$D$92,A29)</f>
+        <f aca="false">COUNTIF('Daftar Peserta'!$D$5:$D$96,A29)</f>
         <v>1</v>
       </c>
     </row>
@@ -1740,7 +1773,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="6" t="n">
-        <f aca="false">COUNTIF('Daftar Peserta'!$D$5:$D$92,A30)</f>
+        <f aca="false">COUNTIF('Daftar Peserta'!$D$5:$D$96,A30)</f>
         <v>1</v>
       </c>
     </row>
@@ -1749,7 +1782,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="6" t="n">
-        <f aca="false">COUNTIF('Daftar Peserta'!$D$5:$D$92,A31)</f>
+        <f aca="false">COUNTIF('Daftar Peserta'!$D$5:$D$96,A31)</f>
         <v>15</v>
       </c>
     </row>
@@ -1806,7 +1839,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M92"/>
+  <dimension ref="A1:M96"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
@@ -2687,7 +2720,7 @@
         <v>128</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>24</v>
@@ -2699,13 +2732,13 @@
         <v>129</v>
       </c>
       <c r="G25" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="I25" s="10" t="s">
         <v>130</v>
-      </c>
-      <c r="H25" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="I25" s="10" t="s">
-        <v>113</v>
       </c>
       <c r="J25" s="10" t="n">
         <v>1</v>
@@ -2715,37 +2748,39 @@
       </c>
       <c r="L25" s="10" t="str">
         <f aca="false">IF(OR(J25="",H25="(belum memilih)",H25="(organik)"),"",IF(OR(H25="7 &amp; 8 Okt",H25="(kosong)",AND(H25="7 Okt",J25=1),AND(H25="8 Okt",J25=2)),"Ya","Tidak"))</f>
-        <v>Tidak</v>
-      </c>
-      <c r="M25" s="5"/>
+        <v/>
+      </c>
+      <c r="M25" s="5" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="10" t="n">
         <v>22</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>24</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>69</v>
+        <v>115</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>71</v>
+        <v>113</v>
       </c>
       <c r="J26" s="10" t="n">
         <v>1</v>
@@ -2755,7 +2790,7 @@
       </c>
       <c r="L26" s="10" t="str">
         <f aca="false">IF(OR(J26="",H26="(belum memilih)",H26="(organik)"),"",IF(OR(H26="7 &amp; 8 Okt",H26="(kosong)",AND(H26="7 Okt",J26=1),AND(H26="8 Okt",J26=2)),"Ya","Tidak"))</f>
-        <v>Ya</v>
+        <v>Tidak</v>
       </c>
       <c r="M26" s="5"/>
     </row>
@@ -2764,25 +2799,25 @@
         <v>23</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>51</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E27" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="G27" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="F27" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="G27" s="5" t="s">
-        <v>130</v>
-      </c>
       <c r="H27" s="5" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="I27" s="10" t="s">
         <v>71</v>
@@ -2804,22 +2839,22 @@
         <v>24</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>51</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>69</v>
+        <v>138</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H28" s="5" t="s">
         <v>55</v>
@@ -2844,48 +2879,50 @@
         <v>25</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>139</v>
+        <v>51</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E29" s="5"/>
-      <c r="F29" s="5"/>
+        <v>24</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>141</v>
+      </c>
       <c r="G29" s="5" t="s">
-        <v>10</v>
+        <v>134</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="J29" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K29" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L29" s="10" t="str">
         <f aca="false">IF(OR(J29="",H29="(belum memilih)",H29="(organik)"),"",IF(OR(H29="7 &amp; 8 Okt",H29="(kosong)",AND(H29="7 Okt",J29=1),AND(H29="8 Okt",J29=2)),"Ya","Tidak"))</f>
-        <v/>
-      </c>
-      <c r="M29" s="5" t="s">
-        <v>140</v>
-      </c>
+        <v>Ya</v>
+      </c>
+      <c r="M29" s="5"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="10" t="n">
         <v>26</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>21</v>
@@ -2912,7 +2949,7 @@
         <v/>
       </c>
       <c r="M30" s="5" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2920,28 +2957,24 @@
         <v>27</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>63</v>
+        <v>143</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="F31" s="5" t="s">
-        <v>143</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="E31" s="5"/>
+      <c r="F31" s="5"/>
       <c r="G31" s="5" t="s">
-        <v>144</v>
+        <v>10</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="I31" s="10" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="J31" s="10" t="n">
         <v>2</v>
@@ -2951,34 +2984,36 @@
       </c>
       <c r="L31" s="10" t="str">
         <f aca="false">IF(OR(J31="",H31="(belum memilih)",H31="(organik)"),"",IF(OR(H31="7 &amp; 8 Okt",H31="(kosong)",AND(H31="7 Okt",J31=1),AND(H31="8 Okt",J31=2)),"Ya","Tidak"))</f>
-        <v>Ya</v>
-      </c>
-      <c r="M31" s="5"/>
+        <v/>
+      </c>
+      <c r="M31" s="5" t="s">
+        <v>144</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="10" t="n">
         <v>28</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="I32" s="10" t="s">
         <v>71</v>
@@ -3000,25 +3035,25 @@
         <v>29</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="F33" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="G33" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="G33" s="5" t="s">
-        <v>149</v>
-      </c>
       <c r="H33" s="5" t="s">
-        <v>55</v>
+        <v>91</v>
       </c>
       <c r="I33" s="10" t="s">
         <v>71</v>
@@ -3031,7 +3066,7 @@
       </c>
       <c r="L33" s="10" t="str">
         <f aca="false">IF(OR(J33="",H33="(belum memilih)",H33="(organik)"),"",IF(OR(H33="7 &amp; 8 Okt",H33="(kosong)",AND(H33="7 Okt",J33=1),AND(H33="8 Okt",J33=2)),"Ya","Tidak"))</f>
-        <v>Tidak</v>
+        <v>Ya</v>
       </c>
       <c r="M33" s="5"/>
     </row>
@@ -3040,28 +3075,28 @@
         <v>30</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>151</v>
+        <v>81</v>
       </c>
       <c r="F34" s="5" t="s">
         <v>152</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>91</v>
+        <v>55</v>
       </c>
       <c r="I34" s="10" t="s">
-        <v>153</v>
+        <v>71</v>
       </c>
       <c r="J34" s="10" t="n">
         <v>2</v>
@@ -3071,7 +3106,7 @@
       </c>
       <c r="L34" s="10" t="str">
         <f aca="false">IF(OR(J34="",H34="(belum memilih)",H34="(organik)"),"",IF(OR(H34="7 &amp; 8 Okt",H34="(kosong)",AND(H34="7 Okt",J34=1),AND(H34="8 Okt",J34=2)),"Ya","Tidak"))</f>
-        <v>Ya</v>
+        <v>Tidak</v>
       </c>
       <c r="M34" s="5"/>
     </row>
@@ -3086,22 +3121,22 @@
         <v>51</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>107</v>
+        <v>155</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="H35" s="5" t="s">
         <v>91</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J35" s="10" t="n">
         <v>2</v>
@@ -3120,28 +3155,28 @@
         <v>32</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C36" s="5" t="s">
         <v>51</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>81</v>
+        <v>107</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>55</v>
+        <v>91</v>
       </c>
       <c r="I36" s="10" t="s">
-        <v>61</v>
+        <v>160</v>
       </c>
       <c r="J36" s="10" t="n">
         <v>2</v>
@@ -3151,7 +3186,7 @@
       </c>
       <c r="L36" s="10" t="str">
         <f aca="false">IF(OR(J36="",H36="(belum memilih)",H36="(organik)"),"",IF(OR(H36="7 &amp; 8 Okt",H36="(kosong)",AND(H36="7 Okt",J36=1),AND(H36="8 Okt",J36=2)),"Ya","Tidak"))</f>
-        <v>Tidak</v>
+        <v>Ya</v>
       </c>
       <c r="M36" s="5"/>
     </row>
@@ -3160,7 +3195,7 @@
         <v>33</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>51</v>
@@ -3168,18 +3203,20 @@
       <c r="D37" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E37" s="5"/>
+      <c r="E37" s="5" t="s">
+        <v>81</v>
+      </c>
       <c r="F37" s="5" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>91</v>
+        <v>55</v>
       </c>
       <c r="I37" s="10" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="J37" s="10" t="n">
         <v>2</v>
@@ -3189,7 +3226,7 @@
       </c>
       <c r="L37" s="10" t="str">
         <f aca="false">IF(OR(J37="",H37="(belum memilih)",H37="(organik)"),"",IF(OR(H37="7 &amp; 8 Okt",H37="(kosong)",AND(H37="7 Okt",J37=1),AND(H37="8 Okt",J37=2)),"Ya","Tidak"))</f>
-        <v>Ya</v>
+        <v>Tidak</v>
       </c>
       <c r="M37" s="5"/>
     </row>
@@ -3198,28 +3235,26 @@
         <v>34</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E38" s="5" t="s">
-        <v>69</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="E38" s="5"/>
       <c r="F38" s="5" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="I38" s="10" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="J38" s="10" t="n">
         <v>2</v>
@@ -3238,28 +3273,28 @@
         <v>35</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>24</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>165</v>
+        <v>69</v>
       </c>
       <c r="F39" s="5" t="s">
         <v>166</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="I39" s="10" t="s">
-        <v>156</v>
+        <v>71</v>
       </c>
       <c r="J39" s="10" t="n">
         <v>2</v>
@@ -3278,7 +3313,7 @@
         <v>36</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C40" s="5" t="s">
         <v>51</v>
@@ -3287,19 +3322,19 @@
         <v>24</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>69</v>
+        <v>169</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>55</v>
+        <v>91</v>
       </c>
       <c r="I40" s="10" t="s">
-        <v>71</v>
+        <v>160</v>
       </c>
       <c r="J40" s="10" t="n">
         <v>2</v>
@@ -3309,7 +3344,7 @@
       </c>
       <c r="L40" s="10" t="str">
         <f aca="false">IF(OR(J40="",H40="(belum memilih)",H40="(organik)"),"",IF(OR(H40="7 &amp; 8 Okt",H40="(kosong)",AND(H40="7 Okt",J40=1),AND(H40="8 Okt",J40=2)),"Ya","Tidak"))</f>
-        <v>Tidak</v>
+        <v>Ya</v>
       </c>
       <c r="M40" s="5"/>
     </row>
@@ -3318,25 +3353,25 @@
         <v>37</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C41" s="5" t="s">
         <v>51</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>111</v>
+        <v>69</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>91</v>
+        <v>55</v>
       </c>
       <c r="I41" s="10" t="s">
         <v>71</v>
@@ -3349,7 +3384,7 @@
       </c>
       <c r="L41" s="10" t="str">
         <f aca="false">IF(OR(J41="",H41="(belum memilih)",H41="(organik)"),"",IF(OR(H41="7 &amp; 8 Okt",H41="(kosong)",AND(H41="7 Okt",J41=1),AND(H41="8 Okt",J41=2)),"Ya","Tidak"))</f>
-        <v>Ya</v>
+        <v>Tidak</v>
       </c>
       <c r="M41" s="5"/>
     </row>
@@ -3358,7 +3393,7 @@
         <v>38</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C42" s="5" t="s">
         <v>51</v>
@@ -3367,13 +3402,13 @@
         <v>21</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>172</v>
+        <v>111</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="H42" s="5" t="s">
         <v>91</v>
@@ -3398,22 +3433,22 @@
         <v>39</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="D43" s="5" t="s">
         <v>21</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="H43" s="5" t="s">
         <v>91</v>
@@ -3441,7 +3476,7 @@
         <v>178</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="D44" s="5" t="s">
         <v>21</v>
@@ -3453,10 +3488,10 @@
         <v>180</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="H44" s="5" t="s">
-        <v>55</v>
+        <v>91</v>
       </c>
       <c r="I44" s="10" t="s">
         <v>71</v>
@@ -3469,7 +3504,7 @@
       </c>
       <c r="L44" s="10" t="str">
         <f aca="false">IF(OR(J44="",H44="(belum memilih)",H44="(organik)"),"",IF(OR(H44="7 &amp; 8 Okt",H44="(kosong)",AND(H44="7 Okt",J44=1),AND(H44="8 Okt",J44=2)),"Ya","Tidak"))</f>
-        <v>Tidak</v>
+        <v>Ya</v>
       </c>
       <c r="M44" s="5"/>
     </row>
@@ -3478,7 +3513,7 @@
         <v>41</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C45" s="5" t="s">
         <v>51</v>
@@ -3487,16 +3522,16 @@
         <v>21</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="H45" s="5" t="s">
-        <v>91</v>
+        <v>55</v>
       </c>
       <c r="I45" s="10" t="s">
         <v>71</v>
@@ -3509,7 +3544,7 @@
       </c>
       <c r="L45" s="10" t="str">
         <f aca="false">IF(OR(J45="",H45="(belum memilih)",H45="(organik)"),"",IF(OR(H45="7 &amp; 8 Okt",H45="(kosong)",AND(H45="7 Okt",J45=1),AND(H45="8 Okt",J45=2)),"Ya","Tidak"))</f>
-        <v>Ya</v>
+        <v>Tidak</v>
       </c>
       <c r="M45" s="5"/>
     </row>
@@ -3518,7 +3553,7 @@
         <v>42</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C46" s="5" t="s">
         <v>51</v>
@@ -3530,13 +3565,13 @@
         <v>179</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="H46" s="5" t="s">
-        <v>55</v>
+        <v>91</v>
       </c>
       <c r="I46" s="10" t="s">
         <v>71</v>
@@ -3549,7 +3584,7 @@
       </c>
       <c r="L46" s="10" t="str">
         <f aca="false">IF(OR(J46="",H46="(belum memilih)",H46="(organik)"),"",IF(OR(H46="7 &amp; 8 Okt",H46="(kosong)",AND(H46="7 Okt",J46=1),AND(H46="8 Okt",J46=2)),"Ya","Tidak"))</f>
-        <v>Tidak</v>
+        <v>Ya</v>
       </c>
       <c r="M46" s="5"/>
     </row>
@@ -3558,7 +3593,7 @@
         <v>43</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C47" s="5" t="s">
         <v>51</v>
@@ -3567,16 +3602,16 @@
         <v>21</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="H47" s="5" t="s">
-        <v>91</v>
+        <v>55</v>
       </c>
       <c r="I47" s="10" t="s">
         <v>71</v>
@@ -3589,7 +3624,7 @@
       </c>
       <c r="L47" s="10" t="str">
         <f aca="false">IF(OR(J47="",H47="(belum memilih)",H47="(organik)"),"",IF(OR(H47="7 &amp; 8 Okt",H47="(kosong)",AND(H47="7 Okt",J47=1),AND(H47="8 Okt",J47=2)),"Ya","Tidak"))</f>
-        <v>Ya</v>
+        <v>Tidak</v>
       </c>
       <c r="M47" s="5"/>
     </row>
@@ -3598,25 +3633,25 @@
         <v>44</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>81</v>
+        <v>179</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="G48" s="5" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="H48" s="5" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="I48" s="10" t="s">
         <v>71</v>
@@ -3638,28 +3673,28 @@
         <v>45</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C49" s="5" t="s">
         <v>51</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="F49" s="5" t="s">
         <v>192</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="H49" s="5" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="I49" s="10" t="s">
-        <v>193</v>
+        <v>130</v>
       </c>
       <c r="J49" s="10" t="n">
         <v>2</v>
@@ -3669,9 +3704,11 @@
       </c>
       <c r="L49" s="10" t="str">
         <f aca="false">IF(OR(J49="",H49="(belum memilih)",H49="(organik)"),"",IF(OR(H49="7 &amp; 8 Okt",H49="(kosong)",AND(H49="7 Okt",J49=1),AND(H49="8 Okt",J49=2)),"Ya","Tidak"))</f>
-        <v>Ya</v>
-      </c>
-      <c r="M49" s="5"/>
+        <v/>
+      </c>
+      <c r="M49" s="5" t="s">
+        <v>193</v>
+      </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="10" t="n">
@@ -3681,86 +3718,90 @@
         <v>194</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>139</v>
+        <v>63</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E50" s="5"/>
-      <c r="F50" s="5"/>
+        <v>23</v>
+      </c>
+      <c r="E50" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F50" s="5" t="s">
+        <v>195</v>
+      </c>
       <c r="G50" s="5" t="s">
-        <v>10</v>
+        <v>196</v>
       </c>
       <c r="H50" s="5" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="I50" s="10" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="J50" s="10" t="n">
         <v>2</v>
       </c>
       <c r="K50" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L50" s="10" t="str">
         <f aca="false">IF(OR(J50="",H50="(belum memilih)",H50="(organik)"),"",IF(OR(H50="7 &amp; 8 Okt",H50="(kosong)",AND(H50="7 Okt",J50=1),AND(H50="8 Okt",J50=2)),"Ya","Tidak"))</f>
-        <v/>
-      </c>
-      <c r="M50" s="5" t="s">
-        <v>140</v>
-      </c>
+        <v>Ya</v>
+      </c>
+      <c r="M50" s="5"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="10" t="n">
         <v>47</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>139</v>
+        <v>51</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E51" s="5"/>
-      <c r="F51" s="5"/>
+        <v>29</v>
+      </c>
+      <c r="E51" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="F51" s="5" t="s">
+        <v>199</v>
+      </c>
       <c r="G51" s="5" t="s">
-        <v>10</v>
+        <v>196</v>
       </c>
       <c r="H51" s="5" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="I51" s="10" t="s">
-        <v>75</v>
+        <v>200</v>
       </c>
       <c r="J51" s="10" t="n">
         <v>2</v>
       </c>
       <c r="K51" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L51" s="10" t="str">
         <f aca="false">IF(OR(J51="",H51="(belum memilih)",H51="(organik)"),"",IF(OR(H51="7 &amp; 8 Okt",H51="(kosong)",AND(H51="7 Okt",J51=1),AND(H51="8 Okt",J51=2)),"Ya","Tidak"))</f>
-        <v/>
-      </c>
-      <c r="M51" s="5" t="s">
-        <v>140</v>
-      </c>
+        <v>Ya</v>
+      </c>
+      <c r="M51" s="5"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="10" t="n">
         <v>48</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>197</v>
+        <v>24</v>
       </c>
       <c r="E52" s="5"/>
       <c r="F52" s="5"/>
@@ -3784,7 +3825,7 @@
         <v/>
       </c>
       <c r="M52" s="5" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3792,28 +3833,24 @@
         <v>49</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>63</v>
+        <v>143</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E53" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="F53" s="5" t="s">
-        <v>200</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="E53" s="5"/>
+      <c r="F53" s="5"/>
       <c r="G53" s="5" t="s">
-        <v>201</v>
+        <v>10</v>
       </c>
       <c r="H53" s="5" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="I53" s="10" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="J53" s="10" t="n">
         <v>2</v>
@@ -3823,37 +3860,35 @@
       </c>
       <c r="L53" s="10" t="str">
         <f aca="false">IF(OR(J53="",H53="(belum memilih)",H53="(organik)"),"",IF(OR(H53="7 &amp; 8 Okt",H53="(kosong)",AND(H53="7 Okt",J53=1),AND(H53="8 Okt",J53=2)),"Ya","Tidak"))</f>
-        <v>Ya</v>
-      </c>
-      <c r="M53" s="5"/>
+        <v/>
+      </c>
+      <c r="M53" s="5" t="s">
+        <v>144</v>
+      </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="10" t="n">
         <v>50</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>51</v>
+        <v>143</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E54" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="F54" s="5" t="s">
         <v>204</v>
       </c>
+      <c r="E54" s="5"/>
+      <c r="F54" s="5"/>
       <c r="G54" s="5" t="s">
-        <v>201</v>
+        <v>10</v>
       </c>
       <c r="H54" s="5" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="I54" s="10" t="s">
-        <v>156</v>
+        <v>75</v>
       </c>
       <c r="J54" s="10" t="n">
         <v>2</v>
@@ -3863,9 +3898,11 @@
       </c>
       <c r="L54" s="10" t="str">
         <f aca="false">IF(OR(J54="",H54="(belum memilih)",H54="(organik)"),"",IF(OR(H54="7 &amp; 8 Okt",H54="(kosong)",AND(H54="7 Okt",J54=1),AND(H54="8 Okt",J54=2)),"Ya","Tidak"))</f>
-        <v>Ya</v>
-      </c>
-      <c r="M54" s="5"/>
+        <v/>
+      </c>
+      <c r="M54" s="5" t="s">
+        <v>144</v>
+      </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="10" t="n">
@@ -3875,25 +3912,25 @@
         <v>205</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="D55" s="5" t="s">
         <v>29</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G55" s="5" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="H55" s="5" t="s">
         <v>91</v>
       </c>
       <c r="I55" s="10" t="s">
-        <v>103</v>
+        <v>71</v>
       </c>
       <c r="J55" s="10" t="n">
         <v>2</v>
@@ -3912,7 +3949,7 @@
         <v>52</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C56" s="5" t="s">
         <v>51</v>
@@ -3921,19 +3958,19 @@
         <v>29</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="F56" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="G56" s="5" t="s">
         <v>208</v>
-      </c>
-      <c r="G56" s="5" t="s">
-        <v>201</v>
       </c>
       <c r="H56" s="5" t="s">
         <v>91</v>
       </c>
       <c r="I56" s="10" t="s">
-        <v>71</v>
+        <v>160</v>
       </c>
       <c r="J56" s="10" t="n">
         <v>2</v>
@@ -3952,28 +3989,28 @@
         <v>53</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>165</v>
+        <v>206</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="G57" s="5" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="H57" s="5" t="s">
         <v>91</v>
       </c>
       <c r="I57" s="10" t="s">
-        <v>71</v>
+        <v>103</v>
       </c>
       <c r="J57" s="10" t="n">
         <v>2</v>
@@ -3992,22 +4029,22 @@
         <v>54</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C58" s="5" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>172</v>
+        <v>206</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="G58" s="5" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="H58" s="5" t="s">
         <v>91</v>
@@ -4032,22 +4069,22 @@
         <v>55</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="H59" s="5" t="s">
         <v>91</v>
@@ -4072,7 +4109,7 @@
         <v>56</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C60" s="5" t="s">
         <v>51</v>
@@ -4081,16 +4118,16 @@
         <v>21</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="G60" s="5" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="H60" s="5" t="s">
-        <v>55</v>
+        <v>91</v>
       </c>
       <c r="I60" s="10" t="s">
         <v>71</v>
@@ -4103,7 +4140,7 @@
       </c>
       <c r="L60" s="10" t="str">
         <f aca="false">IF(OR(J60="",H60="(belum memilih)",H60="(organik)"),"",IF(OR(H60="7 &amp; 8 Okt",H60="(kosong)",AND(H60="7 Okt",J60=1),AND(H60="8 Okt",J60=2)),"Ya","Tidak"))</f>
-        <v>Tidak</v>
+        <v>Ya</v>
       </c>
       <c r="M60" s="5"/>
     </row>
@@ -4112,7 +4149,7 @@
         <v>57</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C61" s="5" t="s">
         <v>51</v>
@@ -4121,19 +4158,19 @@
         <v>21</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="G61" s="5" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="H61" s="5" t="s">
-        <v>55</v>
+        <v>91</v>
       </c>
       <c r="I61" s="10" t="s">
-        <v>113</v>
+        <v>71</v>
       </c>
       <c r="J61" s="10" t="n">
         <v>2</v>
@@ -4143,7 +4180,7 @@
       </c>
       <c r="L61" s="10" t="str">
         <f aca="false">IF(OR(J61="",H61="(belum memilih)",H61="(organik)"),"",IF(OR(H61="7 &amp; 8 Okt",H61="(kosong)",AND(H61="7 Okt",J61=1),AND(H61="8 Okt",J61=2)),"Ya","Tidak"))</f>
-        <v>Tidak</v>
+        <v>Ya</v>
       </c>
       <c r="M61" s="5"/>
     </row>
@@ -4152,28 +4189,28 @@
         <v>58</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>115</v>
+        <v>183</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="G62" s="5" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="H62" s="5" t="s">
-        <v>91</v>
+        <v>55</v>
       </c>
       <c r="I62" s="10" t="s">
-        <v>223</v>
+        <v>71</v>
       </c>
       <c r="J62" s="10" t="n">
         <v>2</v>
@@ -4183,7 +4220,7 @@
       </c>
       <c r="L62" s="10" t="str">
         <f aca="false">IF(OR(J62="",H62="(belum memilih)",H62="(organik)"),"",IF(OR(H62="7 &amp; 8 Okt",H62="(kosong)",AND(H62="7 Okt",J62=1),AND(H62="8 Okt",J62=2)),"Ya","Tidak"))</f>
-        <v>Ya</v>
+        <v>Tidak</v>
       </c>
       <c r="M62" s="5"/>
     </row>
@@ -4192,28 +4229,28 @@
         <v>59</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C63" s="5" t="s">
         <v>51</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>225</v>
+        <v>176</v>
       </c>
       <c r="F63" s="5" t="s">
         <v>226</v>
       </c>
       <c r="G63" s="5" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="H63" s="5" t="s">
-        <v>83</v>
+        <v>55</v>
       </c>
       <c r="I63" s="10" t="s">
-        <v>223</v>
+        <v>113</v>
       </c>
       <c r="J63" s="10" t="n">
         <v>2</v>
@@ -4223,7 +4260,7 @@
       </c>
       <c r="L63" s="10" t="str">
         <f aca="false">IF(OR(J63="",H63="(belum memilih)",H63="(organik)"),"",IF(OR(H63="7 &amp; 8 Okt",H63="(kosong)",AND(H63="7 Okt",J63=1),AND(H63="8 Okt",J63=2)),"Ya","Tidak"))</f>
-        <v>Ya</v>
+        <v>Tidak</v>
       </c>
       <c r="M63" s="5"/>
     </row>
@@ -4235,25 +4272,25 @@
         <v>227</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E64" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="F64" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="F64" s="5" t="s">
+      <c r="G64" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="G64" s="5" t="s">
-        <v>222</v>
-      </c>
       <c r="H64" s="5" t="s">
-        <v>55</v>
+        <v>91</v>
       </c>
       <c r="I64" s="10" t="s">
-        <v>71</v>
+        <v>230</v>
       </c>
       <c r="J64" s="10" t="n">
         <v>2</v>
@@ -4263,7 +4300,7 @@
       </c>
       <c r="L64" s="10" t="str">
         <f aca="false">IF(OR(J64="",H64="(belum memilih)",H64="(organik)"),"",IF(OR(H64="7 &amp; 8 Okt",H64="(kosong)",AND(H64="7 Okt",J64=1),AND(H64="8 Okt",J64=2)),"Ya","Tidak"))</f>
-        <v>Tidak</v>
+        <v>Ya</v>
       </c>
       <c r="M64" s="5"/>
     </row>
@@ -4272,7 +4309,7 @@
         <v>61</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C65" s="5" t="s">
         <v>51</v>
@@ -4281,19 +4318,19 @@
         <v>24</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F65" s="5" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G65" s="5" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="H65" s="5" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="I65" s="10" t="s">
-        <v>118</v>
+        <v>230</v>
       </c>
       <c r="J65" s="10" t="n">
         <v>2</v>
@@ -4312,25 +4349,25 @@
         <v>62</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C66" s="5" t="s">
         <v>51</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>69</v>
+        <v>235</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="G66" s="5" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="H66" s="5" t="s">
-        <v>91</v>
+        <v>55</v>
       </c>
       <c r="I66" s="10" t="s">
         <v>71</v>
@@ -4343,7 +4380,7 @@
       </c>
       <c r="L66" s="10" t="str">
         <f aca="false">IF(OR(J66="",H66="(belum memilih)",H66="(organik)"),"",IF(OR(H66="7 &amp; 8 Okt",H66="(kosong)",AND(H66="7 Okt",J66=1),AND(H66="8 Okt",J66=2)),"Ya","Tidak"))</f>
-        <v>Ya</v>
+        <v>Tidak</v>
       </c>
       <c r="M66" s="5"/>
     </row>
@@ -4352,28 +4389,28 @@
         <v>63</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="D67" s="5" t="s">
         <v>24</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>115</v>
+        <v>238</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="G67" s="5" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="H67" s="5" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="I67" s="10" t="s">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="J67" s="10" t="n">
         <v>2</v>
@@ -4392,28 +4429,28 @@
         <v>64</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C68" s="5" t="s">
         <v>51</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>111</v>
+        <v>69</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="G68" s="5" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="H68" s="5" t="s">
         <v>91</v>
       </c>
       <c r="I68" s="10" t="s">
-        <v>240</v>
+        <v>71</v>
       </c>
       <c r="J68" s="10" t="n">
         <v>2</v>
@@ -4432,28 +4469,28 @@
         <v>65</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>228</v>
+        <v>115</v>
       </c>
       <c r="F69" s="5" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G69" s="5" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="H69" s="5" t="s">
         <v>83</v>
       </c>
       <c r="I69" s="10" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="J69" s="10" t="n">
         <v>2</v>
@@ -4472,28 +4509,28 @@
         <v>66</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C70" s="5" t="s">
         <v>51</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>69</v>
+        <v>111</v>
       </c>
       <c r="F70" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="G70" s="5" t="s">
         <v>244</v>
-      </c>
-      <c r="G70" s="5" t="s">
-        <v>237</v>
       </c>
       <c r="H70" s="5" t="s">
         <v>91</v>
       </c>
       <c r="I70" s="10" t="s">
-        <v>71</v>
+        <v>247</v>
       </c>
       <c r="J70" s="10" t="n">
         <v>2</v>
@@ -4512,113 +4549,121 @@
         <v>67</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>139</v>
+        <v>51</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E71" s="5"/>
-      <c r="F71" s="5"/>
+        <v>22</v>
+      </c>
+      <c r="E71" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="F71" s="5" t="s">
+        <v>249</v>
+      </c>
       <c r="G71" s="5" t="s">
-        <v>10</v>
+        <v>244</v>
       </c>
       <c r="H71" s="5" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="I71" s="10" t="s">
-        <v>75</v>
+        <v>113</v>
       </c>
       <c r="J71" s="10" t="n">
         <v>2</v>
       </c>
       <c r="K71" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L71" s="10" t="str">
         <f aca="false">IF(OR(J71="",H71="(belum memilih)",H71="(organik)"),"",IF(OR(H71="7 &amp; 8 Okt",H71="(kosong)",AND(H71="7 Okt",J71=1),AND(H71="8 Okt",J71=2)),"Ya","Tidak"))</f>
-        <v/>
-      </c>
-      <c r="M71" s="5" t="s">
-        <v>140</v>
-      </c>
+        <v>Ya</v>
+      </c>
+      <c r="M71" s="5"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="10" t="n">
         <v>68</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>139</v>
+        <v>51</v>
       </c>
       <c r="D72" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E72" s="5"/>
-      <c r="F72" s="5"/>
+      <c r="E72" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="F72" s="5" t="s">
+        <v>251</v>
+      </c>
       <c r="G72" s="5" t="s">
-        <v>10</v>
+        <v>244</v>
       </c>
       <c r="H72" s="5" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="I72" s="10" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="J72" s="10" t="n">
         <v>2</v>
       </c>
       <c r="K72" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L72" s="10" t="str">
         <f aca="false">IF(OR(J72="",H72="(belum memilih)",H72="(organik)"),"",IF(OR(H72="7 &amp; 8 Okt",H72="(kosong)",AND(H72="7 Okt",J72=1),AND(H72="8 Okt",J72=2)),"Ya","Tidak"))</f>
-        <v/>
-      </c>
-      <c r="M72" s="5" t="s">
-        <v>140</v>
-      </c>
+        <v>Ya</v>
+      </c>
+      <c r="M72" s="5"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="10" t="n">
         <v>69</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>139</v>
+        <v>204</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="E73" s="5"/>
-      <c r="F73" s="5"/>
+        <v>24</v>
+      </c>
+      <c r="E73" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="F73" s="5" t="s">
+        <v>253</v>
+      </c>
       <c r="G73" s="5" t="s">
-        <v>10</v>
+        <v>54</v>
       </c>
       <c r="H73" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I73" s="10" t="s">
-        <v>75</v>
+        <v>130</v>
       </c>
       <c r="J73" s="10" t="n">
         <v>2</v>
       </c>
       <c r="K73" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L73" s="10" t="str">
         <f aca="false">IF(OR(J73="",H73="(belum memilih)",H73="(organik)"),"",IF(OR(H73="7 &amp; 8 Okt",H73="(kosong)",AND(H73="7 Okt",J73=1),AND(H73="8 Okt",J73=2)),"Ya","Tidak"))</f>
         <v/>
       </c>
       <c r="M73" s="5" t="s">
-        <v>140</v>
+        <v>254</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4626,28 +4671,24 @@
         <v>70</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>51</v>
+        <v>143</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E74" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="F74" s="5" t="s">
-        <v>249</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="E74" s="5"/>
+      <c r="F74" s="5"/>
       <c r="G74" s="5" t="s">
-        <v>54</v>
+        <v>10</v>
       </c>
       <c r="H74" s="5" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="I74" s="10" t="s">
-        <v>156</v>
+        <v>75</v>
       </c>
       <c r="J74" s="10" t="n">
         <v>2</v>
@@ -4657,10 +4698,10 @@
       </c>
       <c r="L74" s="10" t="str">
         <f aca="false">IF(OR(J74="",H74="(belum memilih)",H74="(organik)"),"",IF(OR(H74="7 &amp; 8 Okt",H74="(kosong)",AND(H74="7 Okt",J74=1),AND(H74="8 Okt",J74=2)),"Ya","Tidak"))</f>
-        <v>Ya</v>
+        <v/>
       </c>
       <c r="M74" s="5" t="s">
-        <v>57</v>
+        <v>144</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4668,21 +4709,21 @@
         <v>71</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>63</v>
+        <v>143</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E75" s="5"/>
       <c r="F75" s="5"/>
       <c r="G75" s="5" t="s">
-        <v>251</v>
+        <v>10</v>
       </c>
       <c r="H75" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I75" s="10" t="s">
         <v>75</v>
@@ -4698,7 +4739,7 @@
         <v/>
       </c>
       <c r="M75" s="5" t="s">
-        <v>76</v>
+        <v>144</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4706,28 +4747,24 @@
         <v>72</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>51</v>
+        <v>143</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E76" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="F76" s="5" t="s">
-        <v>254</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="E76" s="5"/>
+      <c r="F76" s="5"/>
       <c r="G76" s="5" t="s">
-        <v>251</v>
+        <v>10</v>
       </c>
       <c r="H76" s="5" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="I76" s="10" t="s">
-        <v>255</v>
+        <v>75</v>
       </c>
       <c r="J76" s="10" t="n">
         <v>2</v>
@@ -4737,37 +4774,39 @@
       </c>
       <c r="L76" s="10" t="str">
         <f aca="false">IF(OR(J76="",H76="(belum memilih)",H76="(organik)"),"",IF(OR(H76="7 &amp; 8 Okt",H76="(kosong)",AND(H76="7 Okt",J76=1),AND(H76="8 Okt",J76=2)),"Ya","Tidak"))</f>
-        <v>Ya</v>
-      </c>
-      <c r="M76" s="5"/>
+        <v/>
+      </c>
+      <c r="M76" s="5" t="s">
+        <v>144</v>
+      </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="10" t="n">
         <v>73</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C77" s="5" t="s">
         <v>51</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>257</v>
+        <v>81</v>
       </c>
       <c r="F77" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="G77" s="5" t="s">
-        <v>251</v>
+        <v>54</v>
       </c>
       <c r="H77" s="5" t="s">
         <v>83</v>
       </c>
       <c r="I77" s="10" t="s">
-        <v>71</v>
+        <v>160</v>
       </c>
       <c r="J77" s="10" t="n">
         <v>2</v>
@@ -4779,35 +4818,33 @@
         <f aca="false">IF(OR(J77="",H77="(belum memilih)",H77="(organik)"),"",IF(OR(H77="7 &amp; 8 Okt",H77="(kosong)",AND(H77="7 Okt",J77=1),AND(H77="8 Okt",J77=2)),"Ya","Tidak"))</f>
         <v>Ya</v>
       </c>
-      <c r="M77" s="5"/>
+      <c r="M77" s="5" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="10" t="n">
         <v>74</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E78" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="F78" s="5" t="s">
-        <v>260</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="E78" s="5"/>
+      <c r="F78" s="5"/>
       <c r="G78" s="5" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="H78" s="5" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="I78" s="10" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="J78" s="10" t="n">
         <v>2</v>
@@ -4817,37 +4854,39 @@
       </c>
       <c r="L78" s="10" t="str">
         <f aca="false">IF(OR(J78="",H78="(belum memilih)",H78="(organik)"),"",IF(OR(H78="7 &amp; 8 Okt",H78="(kosong)",AND(H78="7 Okt",J78=1),AND(H78="8 Okt",J78=2)),"Ya","Tidak"))</f>
-        <v>Ya</v>
-      </c>
-      <c r="M78" s="5"/>
+        <v/>
+      </c>
+      <c r="M78" s="5" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="10" t="n">
         <v>75</v>
       </c>
       <c r="B79" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="C79" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D79" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E79" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="F79" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="G79" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="C79" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="D79" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E79" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="F79" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="G79" s="5" t="s">
-        <v>263</v>
-      </c>
       <c r="H79" s="5" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="I79" s="10" t="s">
-        <v>71</v>
+        <v>265</v>
       </c>
       <c r="J79" s="10" t="n">
         <v>2</v>
@@ -4857,7 +4896,7 @@
       </c>
       <c r="L79" s="10" t="str">
         <f aca="false">IF(OR(J79="",H79="(belum memilih)",H79="(organik)"),"",IF(OR(H79="7 &amp; 8 Okt",H79="(kosong)",AND(H79="7 Okt",J79=1),AND(H79="8 Okt",J79=2)),"Ya","Tidak"))</f>
-        <v>Tidak</v>
+        <v>Ya</v>
       </c>
       <c r="M79" s="5"/>
     </row>
@@ -4866,28 +4905,28 @@
         <v>76</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C80" s="5" t="s">
         <v>51</v>
       </c>
       <c r="D80" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>78</v>
+        <v>267</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="G80" s="5" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="H80" s="5" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="I80" s="10" t="s">
-        <v>266</v>
+        <v>71</v>
       </c>
       <c r="J80" s="10" t="n">
         <v>2</v>
@@ -4897,7 +4936,7 @@
       </c>
       <c r="L80" s="10" t="str">
         <f aca="false">IF(OR(J80="",H80="(belum memilih)",H80="(organik)"),"",IF(OR(H80="7 &amp; 8 Okt",H80="(kosong)",AND(H80="7 Okt",J80=1),AND(H80="8 Okt",J80=2)),"Ya","Tidak"))</f>
-        <v>Tidak</v>
+        <v>Ya</v>
       </c>
       <c r="M80" s="5"/>
     </row>
@@ -4906,28 +4945,28 @@
         <v>77</v>
       </c>
       <c r="B81" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="C81" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D81" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E81" s="5" t="s">
         <v>267</v>
       </c>
-      <c r="C81" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="D81" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E81" s="5" t="s">
-        <v>203</v>
-      </c>
       <c r="F81" s="5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="G81" s="5" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="H81" s="5" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="I81" s="10" t="s">
-        <v>156</v>
+        <v>71</v>
       </c>
       <c r="J81" s="10" t="n">
         <v>2</v>
@@ -4946,28 +4985,28 @@
         <v>78</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>203</v>
+        <v>81</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="G82" s="5" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="H82" s="5" t="s">
-        <v>91</v>
+        <v>55</v>
       </c>
       <c r="I82" s="10" t="s">
-        <v>156</v>
+        <v>71</v>
       </c>
       <c r="J82" s="10" t="n">
         <v>2</v>
@@ -4977,7 +5016,7 @@
       </c>
       <c r="L82" s="10" t="str">
         <f aca="false">IF(OR(J82="",H82="(belum memilih)",H82="(organik)"),"",IF(OR(H82="7 &amp; 8 Okt",H82="(kosong)",AND(H82="7 Okt",J82=1),AND(H82="8 Okt",J82=2)),"Ya","Tidak"))</f>
-        <v>Ya</v>
+        <v>Tidak</v>
       </c>
       <c r="M82" s="5"/>
     </row>
@@ -4986,28 +5025,28 @@
         <v>79</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C83" s="5" t="s">
         <v>51</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>203</v>
+        <v>78</v>
       </c>
       <c r="F83" s="5" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="G83" s="5" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="H83" s="5" t="s">
-        <v>91</v>
+        <v>55</v>
       </c>
       <c r="I83" s="10" t="s">
-        <v>103</v>
+        <v>276</v>
       </c>
       <c r="J83" s="10" t="n">
         <v>2</v>
@@ -5017,7 +5056,7 @@
       </c>
       <c r="L83" s="10" t="str">
         <f aca="false">IF(OR(J83="",H83="(belum memilih)",H83="(organik)"),"",IF(OR(H83="7 &amp; 8 Okt",H83="(kosong)",AND(H83="7 Okt",J83=1),AND(H83="8 Okt",J83=2)),"Ya","Tidak"))</f>
-        <v>Ya</v>
+        <v>Tidak</v>
       </c>
       <c r="M83" s="5"/>
     </row>
@@ -5026,28 +5065,28 @@
         <v>80</v>
       </c>
       <c r="B84" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="C84" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D84" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E84" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="F84" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="G84" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="C84" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="D84" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E84" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="F84" s="5" t="s">
-        <v>274</v>
-      </c>
-      <c r="G84" s="5" t="s">
-        <v>263</v>
-      </c>
       <c r="H84" s="5" t="s">
-        <v>55</v>
+        <v>91</v>
       </c>
       <c r="I84" s="10" t="s">
-        <v>266</v>
+        <v>160</v>
       </c>
       <c r="J84" s="10" t="n">
         <v>2</v>
@@ -5057,7 +5096,7 @@
       </c>
       <c r="L84" s="10" t="str">
         <f aca="false">IF(OR(J84="",H84="(belum memilih)",H84="(organik)"),"",IF(OR(H84="7 &amp; 8 Okt",H84="(kosong)",AND(H84="7 Okt",J84=1),AND(H84="8 Okt",J84=2)),"Ya","Tidak"))</f>
-        <v>Tidak</v>
+        <v>Ya</v>
       </c>
       <c r="M84" s="5"/>
     </row>
@@ -5066,28 +5105,28 @@
         <v>81</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>276</v>
+        <v>210</v>
       </c>
       <c r="F85" s="5" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="G85" s="5" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="H85" s="5" t="s">
         <v>91</v>
       </c>
       <c r="I85" s="10" t="s">
-        <v>67</v>
+        <v>160</v>
       </c>
       <c r="J85" s="10" t="n">
         <v>2</v>
@@ -5106,28 +5145,28 @@
         <v>82</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C86" s="5" t="s">
         <v>51</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G86" s="5" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="H86" s="5" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="I86" s="10" t="s">
-        <v>71</v>
+        <v>103</v>
       </c>
       <c r="J86" s="10" t="n">
         <v>2</v>
@@ -5146,28 +5185,28 @@
         <v>83</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>165</v>
+        <v>78</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="G87" s="5" t="s">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="H87" s="5" t="s">
-        <v>83</v>
+        <v>55</v>
       </c>
       <c r="I87" s="10" t="s">
-        <v>71</v>
+        <v>276</v>
       </c>
       <c r="J87" s="10" t="n">
         <v>2</v>
@@ -5177,7 +5216,7 @@
       </c>
       <c r="L87" s="10" t="str">
         <f aca="false">IF(OR(J87="",H87="(belum memilih)",H87="(organik)"),"",IF(OR(H87="7 &amp; 8 Okt",H87="(kosong)",AND(H87="7 Okt",J87=1),AND(H87="8 Okt",J87=2)),"Ya","Tidak"))</f>
-        <v>Ya</v>
+        <v>Tidak</v>
       </c>
       <c r="M87" s="5"/>
     </row>
@@ -5186,28 +5225,28 @@
         <v>84</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="D88" s="5" t="s">
         <v>24</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>69</v>
+        <v>286</v>
       </c>
       <c r="F88" s="5" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="G88" s="5" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="H88" s="5" t="s">
-        <v>55</v>
+        <v>91</v>
       </c>
       <c r="I88" s="10" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="J88" s="10" t="n">
         <v>2</v>
@@ -5217,7 +5256,7 @@
       </c>
       <c r="L88" s="10" t="str">
         <f aca="false">IF(OR(J88="",H88="(belum memilih)",H88="(organik)"),"",IF(OR(H88="7 &amp; 8 Okt",H88="(kosong)",AND(H88="7 Okt",J88=1),AND(H88="8 Okt",J88=2)),"Ya","Tidak"))</f>
-        <v>Tidak</v>
+        <v>Ya</v>
       </c>
       <c r="M88" s="5"/>
     </row>
@@ -5226,28 +5265,28 @@
         <v>85</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="C89" s="5" t="s">
         <v>51</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>287</v>
+        <v>232</v>
       </c>
       <c r="F89" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="G89" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="G89" s="5" t="s">
-        <v>283</v>
-      </c>
       <c r="H89" s="5" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="I89" s="10" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="J89" s="10" t="n">
         <v>2</v>
@@ -5266,28 +5305,28 @@
         <v>86</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>107</v>
+        <v>169</v>
       </c>
       <c r="F90" s="5" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="G90" s="5" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="H90" s="5" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="I90" s="10" t="s">
-        <v>113</v>
+        <v>71</v>
       </c>
       <c r="J90" s="10" t="n">
         <v>2</v>
@@ -5306,28 +5345,28 @@
         <v>87</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="C91" s="5" t="s">
         <v>51</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>287</v>
+        <v>69</v>
       </c>
       <c r="F91" s="5" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="G91" s="5" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="H91" s="5" t="s">
-        <v>91</v>
+        <v>55</v>
       </c>
       <c r="I91" s="10" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="J91" s="10" t="n">
         <v>2</v>
@@ -5337,50 +5376,208 @@
       </c>
       <c r="L91" s="10" t="str">
         <f aca="false">IF(OR(J91="",H91="(belum memilih)",H91="(organik)"),"",IF(OR(H91="7 &amp; 8 Okt",H91="(kosong)",AND(H91="7 Okt",J91=1),AND(H91="8 Okt",J91=2)),"Ya","Tidak"))</f>
-        <v>Ya</v>
+        <v>Tidak</v>
       </c>
       <c r="M91" s="5"/>
     </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="10" t="n">
         <v>88</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>197</v>
+        <v>51</v>
       </c>
       <c r="D92" s="5" t="s">
         <v>21</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>107</v>
+        <v>297</v>
       </c>
       <c r="F92" s="5" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="G92" s="5" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="H92" s="5" t="s">
         <v>91</v>
       </c>
       <c r="I92" s="10" t="s">
-        <v>223</v>
-      </c>
-      <c r="J92" s="10"/>
-      <c r="K92" s="10"/>
+        <v>67</v>
+      </c>
+      <c r="J92" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K92" s="10" t="n">
+        <v>4</v>
+      </c>
       <c r="L92" s="10" t="str">
         <f aca="false">IF(OR(J92="",H92="(belum memilih)",H92="(organik)"),"",IF(OR(H92="7 &amp; 8 Okt",H92="(kosong)",AND(H92="7 Okt",J92=1),AND(H92="8 Okt",J92=2)),"Ya","Tidak"))</f>
+        <v>Ya</v>
+      </c>
+      <c r="M92" s="5"/>
+    </row>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A93" s="10" t="n">
+        <v>89</v>
+      </c>
+      <c r="B93" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="C93" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D93" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E93" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="F93" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="G93" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="H93" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="I93" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="J93" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K93" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="L93" s="10" t="str">
+        <f aca="false">IF(OR(J93="",H93="(belum memilih)",H93="(organik)"),"",IF(OR(H93="7 &amp; 8 Okt",H93="(kosong)",AND(H93="7 Okt",J93=1),AND(H93="8 Okt",J93=2)),"Ya","Tidak"))</f>
+        <v>Ya</v>
+      </c>
+      <c r="M93" s="5"/>
+    </row>
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A94" s="10" t="n">
+        <v>90</v>
+      </c>
+      <c r="B94" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="C94" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D94" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E94" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="F94" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="G94" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="H94" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="I94" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="J94" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K94" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="L94" s="10" t="str">
+        <f aca="false">IF(OR(J94="",H94="(belum memilih)",H94="(organik)"),"",IF(OR(H94="7 &amp; 8 Okt",H94="(kosong)",AND(H94="7 Okt",J94=1),AND(H94="8 Okt",J94=2)),"Ya","Tidak"))</f>
+        <v>Ya</v>
+      </c>
+      <c r="M94" s="5"/>
+    </row>
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="10" t="n">
+        <v>91</v>
+      </c>
+      <c r="B95" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="C95" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="D95" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E95" s="5"/>
+      <c r="F95" s="5"/>
+      <c r="G95" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="H95" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="I95" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="J95" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K95" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="L95" s="10" t="str">
+        <f aca="false">IF(OR(J95="",H95="(belum memilih)",H95="(organik)"),"",IF(OR(H95="7 &amp; 8 Okt",H95="(kosong)",AND(H95="7 Okt",J95=1),AND(H95="8 Okt",J95=2)),"Ya","Tidak"))</f>
         <v/>
       </c>
-      <c r="M92" s="5" t="s">
-        <v>296</v>
+      <c r="M95" s="5" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="10" t="n">
+        <v>92</v>
+      </c>
+      <c r="B96" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="C96" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="D96" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E96" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="F96" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="G96" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="H96" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="I96" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="J96" s="10"/>
+      <c r="K96" s="10"/>
+      <c r="L96" s="10" t="str">
+        <f aca="false">IF(OR(J92="",H92="(belum memilih)",H92="(organik)"),"",IF(OR(H92="7 &amp; 8 Okt",H92="(kosong)",AND(H92="7 Okt",J92=1),AND(H92="8 Okt",J92=2)),"Ya","Tidak"))</f>
+        <v>Ya</v>
+      </c>
+      <c r="M96" s="5" t="s">
+        <v>307</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:M92"/>
+  <autoFilter ref="A4:M96"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -5412,7 +5609,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>297</v>
+        <v>308</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5423,25 +5620,25 @@
         <v>46</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>298</v>
+        <v>309</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>299</v>
+        <v>310</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>300</v>
+        <v>311</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>302</v>
+        <v>313</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5452,29 +5649,29 @@
         <v>1</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>305</v>
+        <v>316</v>
       </c>
       <c r="D4" s="11" t="n">
-        <f aca="false">COUNTIFS('Daftar Peserta'!$K$5:$K$92,1,'Daftar Peserta'!$C$5:$C$92,"&lt;&gt;SIT-IN")</f>
-        <v>24</v>
+        <f aca="false">COUNTIFS('Daftar Peserta'!$K$5:$K$96,1,'Daftar Peserta'!$C$5:$C$96,"&lt;&gt;SIT-IN")</f>
+        <v>25</v>
       </c>
       <c r="E4" s="11" t="n">
-        <f aca="false">COUNTIFS('Daftar Peserta'!$K$5:$K$92,1,'Daftar Peserta'!$C$5:$C$92,"SIT-IN")</f>
+        <f aca="false">COUNTIFS('Daftar Peserta'!$K$5:$K$96,1,'Daftar Peserta'!$C$5:$C$96,"SIT-IN")</f>
         <v>0</v>
       </c>
       <c r="F4" s="11" t="n">
         <f aca="false">D4+E4</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G4" s="11" t="str">
         <f aca="false">IF(AND(F4&gt;=20,F4&lt;=27),"OK",IF(F4&lt;20,"Kurang "&amp;(20-F4),"Lebih "&amp;(F4-27)))</f>
         <v>OK</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>306</v>
+        <v>317</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>307</v>
+        <v>318</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5485,29 +5682,29 @@
         <v>2</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>308</v>
+        <v>319</v>
       </c>
       <c r="D5" s="11" t="n">
-        <f aca="false">COUNTIFS('Daftar Peserta'!$K$5:$K$92,2,'Daftar Peserta'!$C$5:$C$92,"&lt;&gt;SIT-IN")</f>
-        <v>19</v>
+        <f aca="false">COUNTIFS('Daftar Peserta'!$K$5:$K$96,2,'Daftar Peserta'!$C$5:$C$96,"&lt;&gt;SIT-IN")</f>
+        <v>20</v>
       </c>
       <c r="E5" s="11" t="n">
-        <f aca="false">COUNTIFS('Daftar Peserta'!$K$5:$K$92,2,'Daftar Peserta'!$C$5:$C$92,"SIT-IN")</f>
+        <f aca="false">COUNTIFS('Daftar Peserta'!$K$5:$K$96,2,'Daftar Peserta'!$C$5:$C$96,"SIT-IN")</f>
         <v>2</v>
       </c>
       <c r="F5" s="11" t="n">
         <f aca="false">D5+E5</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G5" s="11" t="str">
         <f aca="false">IF(AND(F5&gt;=20,F5&lt;=27),"OK",IF(F5&lt;20,"Kurang "&amp;(20-F5),"Lebih "&amp;(F5-27)))</f>
         <v>OK</v>
       </c>
       <c r="H5" s="12" t="s">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="I5" s="12" t="s">
-        <v>310</v>
+        <v>321</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5518,29 +5715,29 @@
         <v>2</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>308</v>
+        <v>319</v>
       </c>
       <c r="D6" s="11" t="n">
-        <f aca="false">COUNTIFS('Daftar Peserta'!$K$5:$K$92,3,'Daftar Peserta'!$C$5:$C$92,"&lt;&gt;SIT-IN")</f>
-        <v>18</v>
+        <f aca="false">COUNTIFS('Daftar Peserta'!$K$5:$K$96,3,'Daftar Peserta'!$C$5:$C$96,"&lt;&gt;SIT-IN")</f>
+        <v>19</v>
       </c>
       <c r="E6" s="11" t="n">
-        <f aca="false">COUNTIFS('Daftar Peserta'!$K$5:$K$92,3,'Daftar Peserta'!$C$5:$C$92,"SIT-IN")</f>
+        <f aca="false">COUNTIFS('Daftar Peserta'!$K$5:$K$96,3,'Daftar Peserta'!$C$5:$C$96,"SIT-IN")</f>
         <v>3</v>
       </c>
       <c r="F6" s="11" t="n">
         <f aca="false">D6+E6</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G6" s="11" t="str">
         <f aca="false">IF(AND(F6&gt;=20,F6&lt;=27),"OK",IF(F6&lt;20,"Kurang "&amp;(20-F6),"Lebih "&amp;(F6-27)))</f>
         <v>OK</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="I6" s="12" t="s">
-        <v>312</v>
+        <v>323</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5551,38 +5748,38 @@
         <v>2</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>308</v>
+        <v>319</v>
       </c>
       <c r="D7" s="11" t="n">
-        <f aca="false">COUNTIFS('Daftar Peserta'!$K$5:$K$92,4,'Daftar Peserta'!$C$5:$C$92,"&lt;&gt;SIT-IN")</f>
-        <v>18</v>
+        <f aca="false">COUNTIFS('Daftar Peserta'!$K$5:$K$96,4,'Daftar Peserta'!$C$5:$C$96,"&lt;&gt;SIT-IN")</f>
+        <v>19</v>
       </c>
       <c r="E7" s="11" t="n">
-        <f aca="false">COUNTIFS('Daftar Peserta'!$K$5:$K$92,4,'Daftar Peserta'!$C$5:$C$92,"SIT-IN")</f>
+        <f aca="false">COUNTIFS('Daftar Peserta'!$K$5:$K$96,4,'Daftar Peserta'!$C$5:$C$96,"SIT-IN")</f>
         <v>3</v>
       </c>
       <c r="F7" s="11" t="n">
         <f aca="false">D7+E7</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G7" s="11" t="str">
         <f aca="false">IF(AND(F7&gt;=20,F7&lt;=27),"OK",IF(F7&lt;20,"Kurang "&amp;(20-F7),"Lebih "&amp;(F7-27)))</f>
         <v>OK</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>314</v>
+        <v>325</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="D8" s="14" t="n">
         <f aca="false">SUM(D4:D7)</f>
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E8" s="14" t="n">
         <f aca="false">SUM(E4:E7)</f>
@@ -5590,12 +5787,12 @@
       </c>
       <c r="F8" s="14" t="n">
         <f aca="false">SUM(F4:F7)</f>
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>315</v>
+        <v>326</v>
       </c>
     </row>
   </sheetData>
@@ -5634,231 +5831,231 @@
         <v>47</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>298</v>
+        <v>309</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>316</v>
+        <v>327</v>
       </c>
       <c r="C2" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>305</v>
+        <v>316</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>317</v>
+        <v>328</v>
       </c>
       <c r="C3" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>305</v>
+        <v>316</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>318</v>
+        <v>329</v>
       </c>
       <c r="C4" s="5" t="n">
         <v>2</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>308</v>
+        <v>319</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c r="B5" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>319</v>
-      </c>
-      <c r="C5" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>320</v>
+        <v>331</v>
       </c>
       <c r="C6" s="5" t="n">
         <v>3</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>308</v>
+        <v>319</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>321</v>
+        <v>332</v>
       </c>
       <c r="C7" s="5" t="n">
         <v>3</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>308</v>
+        <v>319</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>4</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>308</v>
+        <v>319</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="C9" s="5" t="n">
         <v>4</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>308</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>300</v>
+        <v>311</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C10" s="5" t="n">
         <v>2</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>308</v>
+        <v>319</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>300</v>
+        <v>311</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C11" s="5" t="n">
         <v>2</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>308</v>
+        <v>319</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>300</v>
+        <v>311</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="C12" s="5" t="n">
         <v>3</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>308</v>
+        <v>319</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>300</v>
+        <v>311</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="C13" s="5" t="n">
         <v>3</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>308</v>
+        <v>319</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>300</v>
+        <v>311</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="C14" s="5" t="n">
         <v>3</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>308</v>
+        <v>319</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>300</v>
+        <v>311</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="C15" s="5" t="n">
         <v>4</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>308</v>
+        <v>319</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>300</v>
+        <v>311</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="C16" s="5" t="n">
         <v>4</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>300</v>
+        <v>311</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="C17" s="5" t="n">
         <v>4</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>308</v>
+        <v>319</v>
       </c>
     </row>
   </sheetData>
@@ -5896,16 +6093,16 @@
         <v>39</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>44</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>326</v>
+        <v>337</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5985,7 +6182,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>327</v>
+        <v>338</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6005,7 +6202,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>327</v>
+        <v>338</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6025,18 +6222,18 @@
         <v>1</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>327</v>
+        <v>338</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="15" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B8" s="15" t="s">
         <v>63</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="D8" s="15" t="s">
         <v>91</v>
@@ -6045,18 +6242,18 @@
         <v>1</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>327</v>
+        <v>338</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B9" s="15" t="s">
         <v>63</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="D9" s="15" t="s">
         <v>55</v>
@@ -6065,18 +6262,18 @@
         <v>2</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>327</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B10" s="15" t="s">
         <v>51</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="D10" s="15" t="s">
         <v>55</v>
@@ -6085,18 +6282,18 @@
         <v>2</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>327</v>
+        <v>338</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="C11" s="15" t="s">
         <v>167</v>
-      </c>
-      <c r="B11" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="C11" s="15" t="s">
-        <v>163</v>
       </c>
       <c r="D11" s="15" t="s">
         <v>55</v>
@@ -6105,18 +6302,18 @@
         <v>2</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>327</v>
+        <v>338</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="15" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B12" s="15" t="s">
         <v>51</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="D12" s="15" t="s">
         <v>55</v>
@@ -6125,18 +6322,18 @@
         <v>2</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>327</v>
+        <v>338</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B13" s="15" t="s">
         <v>51</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="D13" s="15" t="s">
         <v>55</v>
@@ -6145,18 +6342,18 @@
         <v>2</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>327</v>
+        <v>338</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="15" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="B14" s="15" t="s">
         <v>51</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="D14" s="15" t="s">
         <v>55</v>
@@ -6165,18 +6362,18 @@
         <v>2</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>327</v>
+        <v>338</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="15" t="s">
+        <v>225</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="C15" s="15" t="s">
         <v>218</v>
-      </c>
-      <c r="B15" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="C15" s="15" t="s">
-        <v>211</v>
       </c>
       <c r="D15" s="15" t="s">
         <v>55</v>
@@ -6185,18 +6382,18 @@
         <v>2</v>
       </c>
       <c r="F15" s="15" t="s">
-        <v>327</v>
+        <v>338</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="15" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="B16" s="15" t="s">
         <v>51</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="D16" s="15" t="s">
         <v>55</v>
@@ -6205,12 +6402,12 @@
         <v>2</v>
       </c>
       <c r="F16" s="15" t="s">
-        <v>327</v>
+        <v>338</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="B17" s="15" t="s">
         <v>51</v>
@@ -6230,13 +6427,13 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="15" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="B18" s="15" t="s">
         <v>63</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="D18" s="15" t="s">
         <v>55</v>
@@ -6245,18 +6442,18 @@
         <v>2</v>
       </c>
       <c r="F18" s="15" t="s">
-        <v>327</v>
+        <v>338</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="15" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="B19" s="15" t="s">
         <v>51</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="D19" s="15" t="s">
         <v>55</v>
@@ -6265,18 +6462,18 @@
         <v>2</v>
       </c>
       <c r="F19" s="15" t="s">
-        <v>327</v>
+        <v>338</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="15" t="s">
+        <v>283</v>
+      </c>
+      <c r="B20" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="C20" s="15" t="s">
         <v>273</v>
-      </c>
-      <c r="B20" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="C20" s="15" t="s">
-        <v>263</v>
       </c>
       <c r="D20" s="15" t="s">
         <v>55</v>
@@ -6285,18 +6482,18 @@
         <v>2</v>
       </c>
       <c r="F20" s="15" t="s">
-        <v>327</v>
+        <v>338</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="15" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="B21" s="15" t="s">
         <v>51</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="D21" s="15" t="s">
         <v>55</v>
@@ -6305,27 +6502,27 @@
         <v>2</v>
       </c>
       <c r="F21" s="15" t="s">
-        <v>327</v>
+        <v>338</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="15" t="s">
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="D22" s="15" t="s">
         <v>91</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="F22" s="15" t="s">
-        <v>296</v>
+        <v>307</v>
       </c>
     </row>
   </sheetData>

--- a/Claude outputs/Peserta_Pelatihan_Bencana_4Kelas_1-3_6Okt2026.xlsx
+++ b/Claude outputs/Peserta_Pelatihan_Bencana_4Kelas_1-3_6Okt2026.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Perlu Konfirmasi" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Daftar Peserta'!$A$4:$M$96</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Daftar Peserta'!$A$4:$M$97</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="971" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="980" uniqueCount="341">
   <si>
     <t xml:space="preserve">Peserta pelatihan petugas pendataan bencana</t>
   </si>
@@ -128,7 +128,7 @@
     <t xml:space="preserve">2. Pilihan jadwal diambil dari isian petugas (7 Okt / 8 Okt / keduanya). Usulan meminimalkan anggota yang harus pindah dari pilihannya; lihat kolom "Sesuai pilihan?" dan sheet "Perlu Konfirmasi".</t>
   </si>
   <si>
-    <t xml:space="preserve">3. Aturan kelas 20-27 peserta: 83 peserta + 8 sit-in organik (8 Okt) = 91 orang = 4 kelas. Panitia 2 orang per kelas dihitung terpisah. Devi Kardila, Berni Desriyanti, Marvi Gusneriza, dan Leni Marta ditambahkan atas arahan 6 Okt.</t>
+    <t xml:space="preserve">3. Aturan kelas 20-27 peserta: 84 peserta + 8 sit-in organik (8 Okt) = 92 orang = 4 kelas. Panitia 2 orang per kelas dihitung terpisah. Devi Kardila, Berni Desriyanti, Marvi Gusneriza, Leni Marta, dan Nila Sari ditambahkan atas arahan 6 Okt.</t>
   </si>
   <si>
     <t xml:space="preserve">4. Masih ada ± 60 petugas yang sudah konfirmasi tetapi belum masuk grup WA; belum dihitung di sini.</t>
@@ -329,6 +329,15 @@
     <t xml:space="preserve">+6282268555992</t>
   </si>
   <si>
+    <t xml:space="preserve">Leni Marta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(belum bergabung)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ditambahkan 6 Okt (status diterima); PML ditetapkan atas arahan; belum bergabung grup WA</t>
+  </si>
+  <si>
     <t xml:space="preserve">Widya Verawati</t>
   </si>
   <si>
@@ -419,9 +428,6 @@
     <t xml:space="preserve">+6282285034316</t>
   </si>
   <si>
-    <t xml:space="preserve">(belum bergabung)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ditambahkan atas arahan; status database masih menolak. Belum bergabung grup WA</t>
   </si>
   <si>
@@ -563,6 +569,12 @@
     <t xml:space="preserve">+6282171806551</t>
   </si>
   <si>
+    <t xml:space="preserve">Nila sari</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+6283193601031</t>
+  </si>
+  <si>
     <t xml:space="preserve">Irawita</t>
   </si>
   <si>
@@ -791,9 +803,6 @@
     <t xml:space="preserve">+6282285119197</t>
   </si>
   <si>
-    <t xml:space="preserve">Ditambahkan 6 Okt (status diterima); peran dan PML belum ditentukan; belum bergabung grup WA</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ardial Jaraf</t>
   </si>
   <si>
@@ -938,9 +947,6 @@
     <t xml:space="preserve">+6285763788768</t>
   </si>
   <si>
-    <t xml:space="preserve">Leni Marta</t>
-  </si>
-  <si>
     <t xml:space="preserve">Mirvan Harvia</t>
   </si>
   <si>
@@ -983,7 +989,7 @@
     <t xml:space="preserve">Mailani Putri + Arini Alva Syaadah</t>
   </si>
   <si>
-    <t xml:space="preserve">Tanpa PML (2); Dessy Meiyarni (2); Hariston (PML organik) (3); Rifa Amelia (PML, menolak) (1); Widya Elvera (4); Widya Verawati (4); Yurneti (5); Yusnita Susanti (4)</t>
+    <t xml:space="preserve">Tanpa PML (2); Dessy Meiyarni (2); Hariston (PML organik) (3); Rifa Amelia (PML, menolak) (1); Widya Elvera (5); Widya Verawati (4); Yurneti (5); Yusnita Susanti (4)</t>
   </si>
   <si>
     <t xml:space="preserve">8 Okt 2026</t>
@@ -992,19 +998,19 @@
     <t xml:space="preserve">Faisal Siddiq + Dina Marizka</t>
   </si>
   <si>
-    <t xml:space="preserve">Ayu Sepriani (2); Budi Pernandes (5); Ferianto (5); Irawita (6); Megawati (2)</t>
+    <t xml:space="preserve">Ayu Sepriani (2); Budi Pernandes (5); Ferianto (6); Irawita (6); Megawati (2)</t>
   </si>
   <si>
     <t xml:space="preserve">Oryza Maria Ulva + Nurafiza Thamrin</t>
   </si>
   <si>
-    <t xml:space="preserve">Lia Angraini (4); Lucky Melan Sari (5); Mega Nana Yulianti (5); Saputra Ebel Feri (4); Tanpa PML (1)</t>
+    <t xml:space="preserve">Lia Angraini (4); Lucky Melan Sari (5); Mega Nana Yulianti (5); Saputra Ebel Feri (5)</t>
   </si>
   <si>
     <t xml:space="preserve">Alex Kandria + Witria Dasni</t>
   </si>
   <si>
-    <t xml:space="preserve">Tanpa PML (2); Ilham (PML organik) (4); Usyenti (6); Yelli Novita Sari (2); Yeni Siswanti (5)</t>
+    <t xml:space="preserve">Tanpa PML (1); Ilham (PML organik) (4); Usyenti (6); Yelli Novita Sari (2); Yeni Siswanti (5)</t>
   </si>
   <si>
     <t xml:space="preserve">Nama panitia pada kolom Panitia adalah USUL (pegawai organik); silakan ganti. Kelas 1 = 7 Okt, kelas 2-4 = 8 Okt.</t>
@@ -1559,8 +1565,8 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="n">
-        <f aca="false">COUNTA('Daftar Peserta'!$B$5:$B$96)</f>
-        <v>92</v>
+        <f aca="false">COUNTA('Daftar Peserta'!$B$5:$B$97)</f>
+        <v>93</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1568,7 +1574,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="n">
-        <f aca="false">COUNTIF('Daftar Peserta'!$C$5:$C$96,"PML")</f>
+        <f aca="false">COUNTIF('Daftar Peserta'!$C$5:$C$97,"PML")</f>
         <v>19</v>
       </c>
     </row>
@@ -1577,8 +1583,8 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="n">
-        <f aca="false">COUNTIF('Daftar Peserta'!$C$5:$C$96,"PPL")</f>
-        <v>62</v>
+        <f aca="false">COUNTIF('Daftar Peserta'!$C$5:$C$97,"PPL")</f>
+        <v>65</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1586,8 +1592,8 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="n">
-        <f aca="false">COUNTIF('Daftar Peserta'!$C$5:$C$96,"-")</f>
-        <v>3</v>
+        <f aca="false">COUNTIF('Daftar Peserta'!$C$5:$C$97,"-")</f>
+        <v>1</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1595,7 +1601,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="n">
-        <f aca="false">COUNTIF('Daftar Peserta'!$M$5:$M$96,"Pegawai organik; di luar*")</f>
+        <f aca="false">COUNTIF('Daftar Peserta'!$M$5:$M$97,"Pegawai organik; di luar*")</f>
         <v>2</v>
       </c>
     </row>
@@ -1604,8 +1610,8 @@
         <v>9</v>
       </c>
       <c r="B10" s="6" t="n">
-        <f aca="false">COUNT('Daftar Peserta'!$K$5:$K$96)</f>
-        <v>91</v>
+        <f aca="false">COUNT('Daftar Peserta'!$K$5:$K$97)</f>
+        <v>92</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1613,7 +1619,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="6" t="n">
-        <f aca="false">COUNTIF('Daftar Peserta'!$C$5:$C$96,"SIT-IN")</f>
+        <f aca="false">COUNTIF('Daftar Peserta'!$C$5:$C$97,"SIT-IN")</f>
         <v>8</v>
       </c>
     </row>
@@ -1622,8 +1628,8 @@
         <v>11</v>
       </c>
       <c r="B12" s="6" t="n">
-        <f aca="false">COUNTIF('Daftar Peserta'!$K$5:$K$96,1)</f>
-        <v>25</v>
+        <f aca="false">COUNTIF('Daftar Peserta'!$K$5:$K$97,1)</f>
+        <v>26</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1631,8 +1637,8 @@
         <v>12</v>
       </c>
       <c r="B13" s="6" t="n">
-        <f aca="false">COUNTIF('Daftar Peserta'!$K$5:$K$96,2)</f>
-        <v>22</v>
+        <f aca="false">COUNTIF('Daftar Peserta'!$K$5:$K$97,2)</f>
+        <v>23</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1640,7 +1646,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="6" t="n">
-        <f aca="false">COUNTIF('Daftar Peserta'!$K$5:$K$96,3)</f>
+        <f aca="false">COUNTIF('Daftar Peserta'!$K$5:$K$97,3)</f>
         <v>22</v>
       </c>
     </row>
@@ -1649,8 +1655,8 @@
         <v>14</v>
       </c>
       <c r="B15" s="6" t="n">
-        <f aca="false">COUNTIF('Daftar Peserta'!$K$5:$K$96,4)</f>
-        <v>22</v>
+        <f aca="false">COUNTIF('Daftar Peserta'!$K$5:$K$97,4)</f>
+        <v>21</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1666,7 +1672,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="6" t="n">
-        <f aca="false">COUNTIF('Daftar Peserta'!$L$5:$L$96,"Tidak")</f>
+        <f aca="false">COUNTIF('Daftar Peserta'!$L$5:$L$97,"Tidak")</f>
         <v>16</v>
       </c>
     </row>
@@ -1675,7 +1681,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="6" t="n">
-        <f aca="false">COUNTIF('Daftar Peserta'!$H$5:$H$96,"7 Okt")</f>
+        <f aca="false">COUNTIF('Daftar Peserta'!$H$5:$H$97,"7 Okt")</f>
         <v>28</v>
       </c>
     </row>
@@ -1684,7 +1690,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="6" t="n">
-        <f aca="false">COUNTIF('Daftar Peserta'!$H$5:$H$96,"8 Okt")</f>
+        <f aca="false">COUNTIF('Daftar Peserta'!$H$5:$H$97,"8 Okt")</f>
         <v>35</v>
       </c>
     </row>
@@ -1693,7 +1699,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="6" t="n">
-        <f aca="false">COUNTIF('Daftar Peserta'!$H$5:$H$96,"7 &amp; 8 Okt")</f>
+        <f aca="false">COUNTIF('Daftar Peserta'!$H$5:$H$97,"7 &amp; 8 Okt")</f>
         <v>15</v>
       </c>
     </row>
@@ -1710,8 +1716,8 @@
         <v>21</v>
       </c>
       <c r="B23" s="6" t="n">
-        <f aca="false">COUNTIF('Daftar Peserta'!$D$5:$D$96,A23)</f>
-        <v>23</v>
+        <f aca="false">COUNTIF('Daftar Peserta'!$D$5:$D$97,A23)</f>
+        <v>24</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1719,7 +1725,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="6" t="n">
-        <f aca="false">COUNTIF('Daftar Peserta'!$D$5:$D$96,A24)</f>
+        <f aca="false">COUNTIF('Daftar Peserta'!$D$5:$D$97,A24)</f>
         <v>2</v>
       </c>
     </row>
@@ -1728,7 +1734,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="6" t="n">
-        <f aca="false">COUNTIF('Daftar Peserta'!$D$5:$D$96,A25)</f>
+        <f aca="false">COUNTIF('Daftar Peserta'!$D$5:$D$97,A25)</f>
         <v>11</v>
       </c>
     </row>
@@ -1737,7 +1743,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="6" t="n">
-        <f aca="false">COUNTIF('Daftar Peserta'!$D$5:$D$96,A26)</f>
+        <f aca="false">COUNTIF('Daftar Peserta'!$D$5:$D$97,A26)</f>
         <v>33</v>
       </c>
     </row>
@@ -1746,7 +1752,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="6" t="n">
-        <f aca="false">COUNTIF('Daftar Peserta'!$D$5:$D$96,A27)</f>
+        <f aca="false">COUNTIF('Daftar Peserta'!$D$5:$D$97,A27)</f>
         <v>3</v>
       </c>
     </row>
@@ -1755,7 +1761,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="6" t="n">
-        <f aca="false">COUNTIF('Daftar Peserta'!$D$5:$D$96,A28)</f>
+        <f aca="false">COUNTIF('Daftar Peserta'!$D$5:$D$97,A28)</f>
         <v>1</v>
       </c>
     </row>
@@ -1764,7 +1770,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="6" t="n">
-        <f aca="false">COUNTIF('Daftar Peserta'!$D$5:$D$96,A29)</f>
+        <f aca="false">COUNTIF('Daftar Peserta'!$D$5:$D$97,A29)</f>
         <v>1</v>
       </c>
     </row>
@@ -1773,7 +1779,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="6" t="n">
-        <f aca="false">COUNTIF('Daftar Peserta'!$D$5:$D$96,A30)</f>
+        <f aca="false">COUNTIF('Daftar Peserta'!$D$5:$D$97,A30)</f>
         <v>1</v>
       </c>
     </row>
@@ -1782,7 +1788,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="6" t="n">
-        <f aca="false">COUNTIF('Daftar Peserta'!$D$5:$D$96,A31)</f>
+        <f aca="false">COUNTIF('Daftar Peserta'!$D$5:$D$97,A31)</f>
         <v>15</v>
       </c>
     </row>
@@ -1839,7 +1845,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M96"/>
+  <dimension ref="A1:M97"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
@@ -2400,25 +2406,21 @@
         <v>100</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E17" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="F17" s="5" t="s">
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="I17" s="10" t="s">
         <v>101</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="H17" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="I17" s="10" t="s">
-        <v>103</v>
       </c>
       <c r="J17" s="10" t="n">
         <v>1</v>
@@ -2428,19 +2430,21 @@
       </c>
       <c r="L17" s="10" t="str">
         <f aca="false">IF(OR(J17="",H17="(belum memilih)",H17="(organik)"),"",IF(OR(H17="7 &amp; 8 Okt",H17="(kosong)",AND(H17="7 Okt",J17=1),AND(H17="8 Okt",J17=2)),"Ya","Tidak"))</f>
-        <v>Ya</v>
-      </c>
-      <c r="M17" s="5"/>
+        <v/>
+      </c>
+      <c r="M17" s="5" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="10" t="n">
         <v>14</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>24</v>
@@ -2449,16 +2453,16 @@
         <v>69</v>
       </c>
       <c r="F18" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="G18" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="G18" s="5" t="s">
-        <v>102</v>
-      </c>
       <c r="H18" s="5" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>71</v>
+        <v>106</v>
       </c>
       <c r="J18" s="10" t="n">
         <v>1</v>
@@ -2477,28 +2481,28 @@
         <v>15</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>51</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>107</v>
+        <v>69</v>
       </c>
       <c r="F19" s="5" t="s">
         <v>108</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="H19" s="5" t="s">
         <v>55</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>109</v>
+        <v>71</v>
       </c>
       <c r="J19" s="10" t="n">
         <v>1</v>
@@ -2517,7 +2521,7 @@
         <v>16</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>51</v>
@@ -2526,19 +2530,19 @@
         <v>21</v>
       </c>
       <c r="E20" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="F20" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="F20" s="5" t="s">
+      <c r="G20" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="I20" s="10" t="s">
         <v>112</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="H20" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="I20" s="10" t="s">
-        <v>113</v>
       </c>
       <c r="J20" s="10" t="n">
         <v>1</v>
@@ -2548,7 +2552,7 @@
       </c>
       <c r="L20" s="10" t="str">
         <f aca="false">IF(OR(J20="",H20="(belum memilih)",H20="(organik)"),"",IF(OR(H20="7 &amp; 8 Okt",H20="(kosong)",AND(H20="7 Okt",J20=1),AND(H20="8 Okt",J20=2)),"Ya","Tidak"))</f>
-        <v>Tidak</v>
+        <v>Ya</v>
       </c>
       <c r="M20" s="5"/>
     </row>
@@ -2557,28 +2561,28 @@
         <v>17</v>
       </c>
       <c r="B21" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E21" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="C21" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E21" s="5" t="s">
+      <c r="F21" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="F21" s="5" t="s">
+      <c r="G21" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="I21" s="10" t="s">
         <v>116</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="H21" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="I21" s="10" t="s">
-        <v>118</v>
       </c>
       <c r="J21" s="10" t="n">
         <v>1</v>
@@ -2588,7 +2592,7 @@
       </c>
       <c r="L21" s="10" t="str">
         <f aca="false">IF(OR(J21="",H21="(belum memilih)",H21="(organik)"),"",IF(OR(H21="7 &amp; 8 Okt",H21="(kosong)",AND(H21="7 Okt",J21=1),AND(H21="8 Okt",J21=2)),"Ya","Tidak"))</f>
-        <v>Ya</v>
+        <v>Tidak</v>
       </c>
       <c r="M21" s="5"/>
     </row>
@@ -2597,22 +2601,22 @@
         <v>18</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>24</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F22" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="G22" s="5" t="s">
         <v>120</v>
-      </c>
-      <c r="G22" s="5" t="s">
-        <v>117</v>
       </c>
       <c r="H22" s="5" t="s">
         <v>55</v>
@@ -2646,19 +2650,19 @@
         <v>24</v>
       </c>
       <c r="E23" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="F23" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="F23" s="5" t="s">
+      <c r="G23" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="I23" s="10" t="s">
         <v>124</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="H23" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="I23" s="10" t="s">
-        <v>125</v>
       </c>
       <c r="J23" s="10" t="n">
         <v>1</v>
@@ -2668,7 +2672,7 @@
       </c>
       <c r="L23" s="10" t="str">
         <f aca="false">IF(OR(J23="",H23="(belum memilih)",H23="(organik)"),"",IF(OR(H23="7 &amp; 8 Okt",H23="(kosong)",AND(H23="7 Okt",J23=1),AND(H23="8 Okt",J23=2)),"Ya","Tidak"))</f>
-        <v>Tidak</v>
+        <v>Ya</v>
       </c>
       <c r="M23" s="5"/>
     </row>
@@ -2677,7 +2681,7 @@
         <v>20</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>51</v>
@@ -2686,19 +2690,19 @@
         <v>24</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="F24" s="5" t="s">
         <v>127</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>55</v>
+        <v>91</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>71</v>
+        <v>128</v>
       </c>
       <c r="J24" s="10" t="n">
         <v>1</v>
@@ -2708,7 +2712,7 @@
       </c>
       <c r="L24" s="10" t="str">
         <f aca="false">IF(OR(J24="",H24="(belum memilih)",H24="(organik)"),"",IF(OR(H24="7 &amp; 8 Okt",H24="(kosong)",AND(H24="7 Okt",J24=1),AND(H24="8 Okt",J24=2)),"Ya","Tidak"))</f>
-        <v>Ya</v>
+        <v>Tidak</v>
       </c>
       <c r="M24" s="5"/>
     </row>
@@ -2717,7 +2721,7 @@
         <v>21</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>51</v>
@@ -2726,19 +2730,19 @@
         <v>24</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>130</v>
+        <v>71</v>
       </c>
       <c r="J25" s="10" t="n">
         <v>1</v>
@@ -2748,39 +2752,37 @@
       </c>
       <c r="L25" s="10" t="str">
         <f aca="false">IF(OR(J25="",H25="(belum memilih)",H25="(organik)"),"",IF(OR(H25="7 &amp; 8 Okt",H25="(kosong)",AND(H25="7 Okt",J25=1),AND(H25="8 Okt",J25=2)),"Ya","Tidak"))</f>
-        <v/>
-      </c>
-      <c r="M25" s="5" t="s">
-        <v>131</v>
-      </c>
+        <v>Ya</v>
+      </c>
+      <c r="M25" s="5"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="10" t="n">
         <v>22</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>24</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="J26" s="10" t="n">
         <v>1</v>
@@ -2790,37 +2792,39 @@
       </c>
       <c r="L26" s="10" t="str">
         <f aca="false">IF(OR(J26="",H26="(belum memilih)",H26="(organik)"),"",IF(OR(H26="7 &amp; 8 Okt",H26="(kosong)",AND(H26="7 Okt",J26=1),AND(H26="8 Okt",J26=2)),"Ya","Tidak"))</f>
-        <v>Tidak</v>
-      </c>
-      <c r="M26" s="5"/>
+        <v/>
+      </c>
+      <c r="M26" s="5" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="10" t="n">
         <v>23</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>24</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>69</v>
+        <v>118</v>
       </c>
       <c r="F27" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="G27" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="G27" s="5" t="s">
-        <v>134</v>
-      </c>
       <c r="H27" s="5" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>71</v>
+        <v>116</v>
       </c>
       <c r="J27" s="10" t="n">
         <v>1</v>
@@ -2830,7 +2834,7 @@
       </c>
       <c r="L27" s="10" t="str">
         <f aca="false">IF(OR(J27="",H27="(belum memilih)",H27="(organik)"),"",IF(OR(H27="7 &amp; 8 Okt",H27="(kosong)",AND(H27="7 Okt",J27=1),AND(H27="8 Okt",J27=2)),"Ya","Tidak"))</f>
-        <v>Ya</v>
+        <v>Tidak</v>
       </c>
       <c r="M27" s="5"/>
     </row>
@@ -2845,19 +2849,19 @@
         <v>51</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E28" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="F28" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="F28" s="5" t="s">
-        <v>139</v>
-      </c>
       <c r="G28" s="5" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="I28" s="10" t="s">
         <v>71</v>
@@ -2879,22 +2883,22 @@
         <v>25</v>
       </c>
       <c r="B29" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E29" s="5" t="s">
         <v>140</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>69</v>
       </c>
       <c r="F29" s="5" t="s">
         <v>141</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H29" s="5" t="s">
         <v>55</v>
@@ -2922,45 +2926,47 @@
         <v>142</v>
       </c>
       <c r="C30" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="F30" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="D30" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E30" s="5"/>
-      <c r="F30" s="5"/>
       <c r="G30" s="5" t="s">
-        <v>10</v>
+        <v>136</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="J30" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K30" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L30" s="10" t="str">
         <f aca="false">IF(OR(J30="",H30="(belum memilih)",H30="(organik)"),"",IF(OR(H30="7 &amp; 8 Okt",H30="(kosong)",AND(H30="7 Okt",J30=1),AND(H30="8 Okt",J30=2)),"Ya","Tidak"))</f>
-        <v/>
-      </c>
-      <c r="M30" s="5" t="s">
-        <v>144</v>
-      </c>
+        <v>Ya</v>
+      </c>
+      <c r="M30" s="5"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="10" t="n">
         <v>27</v>
       </c>
       <c r="B31" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="C31" s="5" t="s">
         <v>145</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>143</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>21</v>
@@ -2987,7 +2993,7 @@
         <v/>
       </c>
       <c r="M31" s="5" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2995,28 +3001,24 @@
         <v>28</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>63</v>
+        <v>145</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E32" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="F32" s="5" t="s">
-        <v>147</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="E32" s="5"/>
+      <c r="F32" s="5"/>
       <c r="G32" s="5" t="s">
-        <v>148</v>
+        <v>10</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="J32" s="10" t="n">
         <v>2</v>
@@ -3026,34 +3028,36 @@
       </c>
       <c r="L32" s="10" t="str">
         <f aca="false">IF(OR(J32="",H32="(belum memilih)",H32="(organik)"),"",IF(OR(H32="7 &amp; 8 Okt",H32="(kosong)",AND(H32="7 Okt",J32=1),AND(H32="8 Okt",J32=2)),"Ya","Tidak"))</f>
-        <v>Ya</v>
-      </c>
-      <c r="M32" s="5"/>
+        <v/>
+      </c>
+      <c r="M32" s="5" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="10" t="n">
         <v>29</v>
       </c>
       <c r="B33" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F33" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="C33" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E33" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="F33" s="5" t="s">
+      <c r="G33" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="G33" s="5" t="s">
-        <v>148</v>
-      </c>
       <c r="H33" s="5" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="I33" s="10" t="s">
         <v>71</v>
@@ -3078,22 +3082,22 @@
         <v>151</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="F34" s="5" t="s">
         <v>152</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>55</v>
+        <v>91</v>
       </c>
       <c r="I34" s="10" t="s">
         <v>71</v>
@@ -3106,7 +3110,7 @@
       </c>
       <c r="L34" s="10" t="str">
         <f aca="false">IF(OR(J34="",H34="(belum memilih)",H34="(organik)"),"",IF(OR(H34="7 &amp; 8 Okt",H34="(kosong)",AND(H34="7 Okt",J34=1),AND(H34="8 Okt",J34=2)),"Ya","Tidak"))</f>
-        <v>Tidak</v>
+        <v>Ya</v>
       </c>
       <c r="M34" s="5"/>
     </row>
@@ -3115,28 +3119,28 @@
         <v>31</v>
       </c>
       <c r="B35" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F35" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="C35" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="E35" s="5" t="s">
+      <c r="G35" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="F35" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="G35" s="5" t="s">
-        <v>153</v>
-      </c>
       <c r="H35" s="5" t="s">
-        <v>91</v>
+        <v>55</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>157</v>
+        <v>71</v>
       </c>
       <c r="J35" s="10" t="n">
         <v>2</v>
@@ -3146,7 +3150,7 @@
       </c>
       <c r="L35" s="10" t="str">
         <f aca="false">IF(OR(J35="",H35="(belum memilih)",H35="(organik)"),"",IF(OR(H35="7 &amp; 8 Okt",H35="(kosong)",AND(H35="7 Okt",J35=1),AND(H35="8 Okt",J35=2)),"Ya","Tidak"))</f>
-        <v>Ya</v>
+        <v>Tidak</v>
       </c>
       <c r="M35" s="5"/>
     </row>
@@ -3155,28 +3159,28 @@
         <v>32</v>
       </c>
       <c r="B36" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="F36" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="C36" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="D36" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E36" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="F36" s="5" t="s">
-        <v>159</v>
-      </c>
       <c r="G36" s="5" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="H36" s="5" t="s">
         <v>91</v>
       </c>
       <c r="I36" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="J36" s="10" t="n">
         <v>2</v>
@@ -3195,28 +3199,28 @@
         <v>33</v>
       </c>
       <c r="B37" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="F37" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="C37" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E37" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="F37" s="5" t="s">
+      <c r="G37" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="H37" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="I37" s="10" t="s">
         <v>162</v>
-      </c>
-      <c r="G37" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="H37" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="I37" s="10" t="s">
-        <v>61</v>
       </c>
       <c r="J37" s="10" t="n">
         <v>2</v>
@@ -3226,7 +3230,7 @@
       </c>
       <c r="L37" s="10" t="str">
         <f aca="false">IF(OR(J37="",H37="(belum memilih)",H37="(organik)"),"",IF(OR(H37="7 &amp; 8 Okt",H37="(kosong)",AND(H37="7 Okt",J37=1),AND(H37="8 Okt",J37=2)),"Ya","Tidak"))</f>
-        <v>Tidak</v>
+        <v>Ya</v>
       </c>
       <c r="M37" s="5"/>
     </row>
@@ -3243,18 +3247,20 @@
       <c r="D38" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E38" s="5"/>
+      <c r="E38" s="5" t="s">
+        <v>81</v>
+      </c>
       <c r="F38" s="5" t="s">
         <v>164</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>91</v>
+        <v>55</v>
       </c>
       <c r="I38" s="10" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="J38" s="10" t="n">
         <v>2</v>
@@ -3264,7 +3270,7 @@
       </c>
       <c r="L38" s="10" t="str">
         <f aca="false">IF(OR(J38="",H38="(belum memilih)",H38="(organik)"),"",IF(OR(H38="7 &amp; 8 Okt",H38="(kosong)",AND(H38="7 Okt",J38=1),AND(H38="8 Okt",J38=2)),"Ya","Tidak"))</f>
-        <v>Ya</v>
+        <v>Tidak</v>
       </c>
       <c r="M38" s="5"/>
     </row>
@@ -3276,25 +3282,23 @@
         <v>165</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E39" s="5" t="s">
-        <v>69</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="E39" s="5"/>
       <c r="F39" s="5" t="s">
         <v>166</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="I39" s="10" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="J39" s="10" t="n">
         <v>2</v>
@@ -3313,28 +3317,28 @@
         <v>36</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="D40" s="5" t="s">
         <v>24</v>
       </c>
       <c r="E40" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="F40" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="G40" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="F40" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="G40" s="5" t="s">
-        <v>167</v>
-      </c>
       <c r="H40" s="5" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="I40" s="10" t="s">
-        <v>160</v>
+        <v>71</v>
       </c>
       <c r="J40" s="10" t="n">
         <v>2</v>
@@ -3353,7 +3357,7 @@
         <v>37</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C41" s="5" t="s">
         <v>51</v>
@@ -3362,19 +3366,19 @@
         <v>24</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>69</v>
+        <v>171</v>
       </c>
       <c r="F41" s="5" t="s">
         <v>172</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>55</v>
+        <v>91</v>
       </c>
       <c r="I41" s="10" t="s">
-        <v>71</v>
+        <v>162</v>
       </c>
       <c r="J41" s="10" t="n">
         <v>2</v>
@@ -3384,7 +3388,7 @@
       </c>
       <c r="L41" s="10" t="str">
         <f aca="false">IF(OR(J41="",H41="(belum memilih)",H41="(organik)"),"",IF(OR(H41="7 &amp; 8 Okt",H41="(kosong)",AND(H41="7 Okt",J41=1),AND(H41="8 Okt",J41=2)),"Ya","Tidak"))</f>
-        <v>Tidak</v>
+        <v>Ya</v>
       </c>
       <c r="M41" s="5"/>
     </row>
@@ -3399,19 +3403,19 @@
         <v>51</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>111</v>
+        <v>69</v>
       </c>
       <c r="F42" s="5" t="s">
         <v>174</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>91</v>
+        <v>55</v>
       </c>
       <c r="I42" s="10" t="s">
         <v>71</v>
@@ -3424,7 +3428,7 @@
       </c>
       <c r="L42" s="10" t="str">
         <f aca="false">IF(OR(J42="",H42="(belum memilih)",H42="(organik)"),"",IF(OR(H42="7 &amp; 8 Okt",H42="(kosong)",AND(H42="7 Okt",J42=1),AND(H42="8 Okt",J42=2)),"Ya","Tidak"))</f>
-        <v>Ya</v>
+        <v>Tidak</v>
       </c>
       <c r="M42" s="5"/>
     </row>
@@ -3442,13 +3446,13 @@
         <v>21</v>
       </c>
       <c r="E43" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="F43" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="F43" s="5" t="s">
-        <v>177</v>
-      </c>
       <c r="G43" s="5" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="H43" s="5" t="s">
         <v>91</v>
@@ -3473,22 +3477,22 @@
         <v>40</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="D44" s="5" t="s">
         <v>21</v>
       </c>
       <c r="E44" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="F44" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="F44" s="5" t="s">
-        <v>180</v>
-      </c>
       <c r="G44" s="5" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="H44" s="5" t="s">
         <v>91</v>
@@ -3513,7 +3517,7 @@
         <v>41</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C45" s="5" t="s">
         <v>51</v>
@@ -3522,19 +3526,19 @@
         <v>21</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>183</v>
+        <v>114</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="H45" s="5" t="s">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="I45" s="10" t="s">
-        <v>71</v>
+        <v>101</v>
       </c>
       <c r="J45" s="10" t="n">
         <v>2</v>
@@ -3544,31 +3548,33 @@
       </c>
       <c r="L45" s="10" t="str">
         <f aca="false">IF(OR(J45="",H45="(belum memilih)",H45="(organik)"),"",IF(OR(H45="7 &amp; 8 Okt",H45="(kosong)",AND(H45="7 Okt",J45=1),AND(H45="8 Okt",J45=2)),"Ya","Tidak"))</f>
-        <v>Tidak</v>
-      </c>
-      <c r="M45" s="5"/>
+        <v/>
+      </c>
+      <c r="M45" s="5" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="10" t="n">
         <v>42</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="D46" s="5" t="s">
         <v>21</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="H46" s="5" t="s">
         <v>91</v>
@@ -3593,7 +3599,7 @@
         <v>43</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C47" s="5" t="s">
         <v>51</v>
@@ -3602,13 +3608,13 @@
         <v>21</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="F47" s="5" t="s">
         <v>188</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="H47" s="5" t="s">
         <v>55</v>
@@ -3642,13 +3648,13 @@
         <v>21</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="F48" s="5" t="s">
         <v>190</v>
       </c>
       <c r="G48" s="5" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="H48" s="5" t="s">
         <v>91</v>
@@ -3682,19 +3688,19 @@
         <v>21</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="F49" s="5" t="s">
         <v>192</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="H49" s="5" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="I49" s="10" t="s">
-        <v>130</v>
+        <v>71</v>
       </c>
       <c r="J49" s="10" t="n">
         <v>2</v>
@@ -3704,36 +3710,34 @@
       </c>
       <c r="L49" s="10" t="str">
         <f aca="false">IF(OR(J49="",H49="(belum memilih)",H49="(organik)"),"",IF(OR(H49="7 &amp; 8 Okt",H49="(kosong)",AND(H49="7 Okt",J49=1),AND(H49="8 Okt",J49=2)),"Ya","Tidak"))</f>
-        <v/>
-      </c>
-      <c r="M49" s="5" t="s">
-        <v>193</v>
-      </c>
+        <v>Tidak</v>
+      </c>
+      <c r="M49" s="5"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="10" t="n">
         <v>46</v>
       </c>
       <c r="B50" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E50" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="F50" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="C50" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="D50" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E50" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="F50" s="5" t="s">
-        <v>195</v>
-      </c>
       <c r="G50" s="5" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="H50" s="5" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="I50" s="10" t="s">
         <v>71</v>
@@ -3755,28 +3759,28 @@
         <v>47</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C51" s="5" t="s">
         <v>51</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>198</v>
+        <v>178</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="H51" s="5" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="I51" s="10" t="s">
-        <v>200</v>
+        <v>101</v>
       </c>
       <c r="J51" s="10" t="n">
         <v>2</v>
@@ -3786,98 +3790,104 @@
       </c>
       <c r="L51" s="10" t="str">
         <f aca="false">IF(OR(J51="",H51="(belum memilih)",H51="(organik)"),"",IF(OR(H51="7 &amp; 8 Okt",H51="(kosong)",AND(H51="7 Okt",J51=1),AND(H51="8 Okt",J51=2)),"Ya","Tidak"))</f>
-        <v>Ya</v>
-      </c>
-      <c r="M51" s="5"/>
+        <v/>
+      </c>
+      <c r="M51" s="5" t="s">
+        <v>197</v>
+      </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="10" t="n">
         <v>48</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>143</v>
+        <v>63</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E52" s="5"/>
-      <c r="F52" s="5"/>
+        <v>23</v>
+      </c>
+      <c r="E52" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F52" s="5" t="s">
+        <v>199</v>
+      </c>
       <c r="G52" s="5" t="s">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c r="H52" s="5" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="I52" s="10" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="J52" s="10" t="n">
         <v>2</v>
       </c>
       <c r="K52" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L52" s="10" t="str">
         <f aca="false">IF(OR(J52="",H52="(belum memilih)",H52="(organik)"),"",IF(OR(H52="7 &amp; 8 Okt",H52="(kosong)",AND(H52="7 Okt",J52=1),AND(H52="8 Okt",J52=2)),"Ya","Tidak"))</f>
-        <v/>
-      </c>
-      <c r="M52" s="5" t="s">
-        <v>144</v>
-      </c>
+        <v>Ya</v>
+      </c>
+      <c r="M52" s="5"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="10" t="n">
         <v>49</v>
       </c>
       <c r="B53" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E53" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="C53" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="D53" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E53" s="5"/>
-      <c r="F53" s="5"/>
+      <c r="F53" s="5" t="s">
+        <v>203</v>
+      </c>
       <c r="G53" s="5" t="s">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c r="H53" s="5" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="I53" s="10" t="s">
-        <v>75</v>
+        <v>204</v>
       </c>
       <c r="J53" s="10" t="n">
         <v>2</v>
       </c>
       <c r="K53" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L53" s="10" t="str">
         <f aca="false">IF(OR(J53="",H53="(belum memilih)",H53="(organik)"),"",IF(OR(H53="7 &amp; 8 Okt",H53="(kosong)",AND(H53="7 Okt",J53=1),AND(H53="8 Okt",J53=2)),"Ya","Tidak"))</f>
-        <v/>
-      </c>
-      <c r="M53" s="5" t="s">
-        <v>144</v>
-      </c>
+        <v>Ya</v>
+      </c>
+      <c r="M53" s="5"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="10" t="n">
         <v>50</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>204</v>
+        <v>24</v>
       </c>
       <c r="E54" s="5"/>
       <c r="F54" s="5"/>
@@ -3901,7 +3911,7 @@
         <v/>
       </c>
       <c r="M54" s="5" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3909,28 +3919,24 @@
         <v>51</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>63</v>
+        <v>145</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E55" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="F55" s="5" t="s">
-        <v>207</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="E55" s="5"/>
+      <c r="F55" s="5"/>
       <c r="G55" s="5" t="s">
-        <v>208</v>
+        <v>10</v>
       </c>
       <c r="H55" s="5" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="I55" s="10" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="J55" s="10" t="n">
         <v>2</v>
@@ -3940,37 +3946,35 @@
       </c>
       <c r="L55" s="10" t="str">
         <f aca="false">IF(OR(J55="",H55="(belum memilih)",H55="(organik)"),"",IF(OR(H55="7 &amp; 8 Okt",H55="(kosong)",AND(H55="7 Okt",J55=1),AND(H55="8 Okt",J55=2)),"Ya","Tidak"))</f>
-        <v>Ya</v>
-      </c>
-      <c r="M55" s="5"/>
+        <v/>
+      </c>
+      <c r="M55" s="5" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="10" t="n">
         <v>52</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>51</v>
+        <v>145</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E56" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="F56" s="5" t="s">
-        <v>211</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="E56" s="5"/>
+      <c r="F56" s="5"/>
       <c r="G56" s="5" t="s">
-        <v>208</v>
+        <v>10</v>
       </c>
       <c r="H56" s="5" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="I56" s="10" t="s">
-        <v>160</v>
+        <v>75</v>
       </c>
       <c r="J56" s="10" t="n">
         <v>2</v>
@@ -3980,37 +3984,39 @@
       </c>
       <c r="L56" s="10" t="str">
         <f aca="false">IF(OR(J56="",H56="(belum memilih)",H56="(organik)"),"",IF(OR(H56="7 &amp; 8 Okt",H56="(kosong)",AND(H56="7 Okt",J56=1),AND(H56="8 Okt",J56=2)),"Ya","Tidak"))</f>
-        <v>Ya</v>
-      </c>
-      <c r="M56" s="5"/>
+        <v/>
+      </c>
+      <c r="M56" s="5" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="10" t="n">
         <v>53</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="D57" s="5" t="s">
         <v>29</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="G57" s="5" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="H57" s="5" t="s">
         <v>91</v>
       </c>
       <c r="I57" s="10" t="s">
-        <v>103</v>
+        <v>71</v>
       </c>
       <c r="J57" s="10" t="n">
         <v>2</v>
@@ -4029,7 +4035,7 @@
         <v>54</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C58" s="5" t="s">
         <v>51</v>
@@ -4038,19 +4044,19 @@
         <v>29</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="F58" s="5" t="s">
         <v>215</v>
       </c>
       <c r="G58" s="5" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="H58" s="5" t="s">
         <v>91</v>
       </c>
       <c r="I58" s="10" t="s">
-        <v>71</v>
+        <v>162</v>
       </c>
       <c r="J58" s="10" t="n">
         <v>2</v>
@@ -4072,25 +4078,25 @@
         <v>216</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>169</v>
+        <v>210</v>
       </c>
       <c r="F59" s="5" t="s">
         <v>217</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="H59" s="5" t="s">
         <v>91</v>
       </c>
       <c r="I59" s="10" t="s">
-        <v>71</v>
+        <v>106</v>
       </c>
       <c r="J59" s="10" t="n">
         <v>2</v>
@@ -4109,22 +4115,22 @@
         <v>56</v>
       </c>
       <c r="B60" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D60" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E60" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="F60" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="C60" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="D60" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E60" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="F60" s="5" t="s">
-        <v>220</v>
-      </c>
       <c r="G60" s="5" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="H60" s="5" t="s">
         <v>91</v>
@@ -4149,22 +4155,22 @@
         <v>57</v>
       </c>
       <c r="B61" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D61" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E61" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="F61" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="C61" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="D61" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E61" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="F61" s="5" t="s">
+      <c r="G61" s="5" t="s">
         <v>222</v>
-      </c>
-      <c r="G61" s="5" t="s">
-        <v>218</v>
       </c>
       <c r="H61" s="5" t="s">
         <v>91</v>
@@ -4198,16 +4204,16 @@
         <v>21</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="F62" s="5" t="s">
         <v>224</v>
       </c>
       <c r="G62" s="5" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="H62" s="5" t="s">
-        <v>55</v>
+        <v>91</v>
       </c>
       <c r="I62" s="10" t="s">
         <v>71</v>
@@ -4220,7 +4226,7 @@
       </c>
       <c r="L62" s="10" t="str">
         <f aca="false">IF(OR(J62="",H62="(belum memilih)",H62="(organik)"),"",IF(OR(H62="7 &amp; 8 Okt",H62="(kosong)",AND(H62="7 Okt",J62=1),AND(H62="8 Okt",J62=2)),"Ya","Tidak"))</f>
-        <v>Tidak</v>
+        <v>Ya</v>
       </c>
       <c r="M62" s="5"/>
     </row>
@@ -4238,19 +4244,19 @@
         <v>21</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F63" s="5" t="s">
         <v>226</v>
       </c>
       <c r="G63" s="5" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="H63" s="5" t="s">
-        <v>55</v>
+        <v>91</v>
       </c>
       <c r="I63" s="10" t="s">
-        <v>113</v>
+        <v>71</v>
       </c>
       <c r="J63" s="10" t="n">
         <v>2</v>
@@ -4260,7 +4266,7 @@
       </c>
       <c r="L63" s="10" t="str">
         <f aca="false">IF(OR(J63="",H63="(belum memilih)",H63="(organik)"),"",IF(OR(H63="7 &amp; 8 Okt",H63="(kosong)",AND(H63="7 Okt",J63=1),AND(H63="8 Okt",J63=2)),"Ya","Tidak"))</f>
-        <v>Tidak</v>
+        <v>Ya</v>
       </c>
       <c r="M63" s="5"/>
     </row>
@@ -4272,25 +4278,25 @@
         <v>227</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>115</v>
+        <v>187</v>
       </c>
       <c r="F64" s="5" t="s">
         <v>228</v>
       </c>
       <c r="G64" s="5" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="H64" s="5" t="s">
-        <v>91</v>
+        <v>55</v>
       </c>
       <c r="I64" s="10" t="s">
-        <v>230</v>
+        <v>71</v>
       </c>
       <c r="J64" s="10" t="n">
         <v>2</v>
@@ -4300,7 +4306,7 @@
       </c>
       <c r="L64" s="10" t="str">
         <f aca="false">IF(OR(J64="",H64="(belum memilih)",H64="(organik)"),"",IF(OR(H64="7 &amp; 8 Okt",H64="(kosong)",AND(H64="7 Okt",J64=1),AND(H64="8 Okt",J64=2)),"Ya","Tidak"))</f>
-        <v>Ya</v>
+        <v>Tidak</v>
       </c>
       <c r="M64" s="5"/>
     </row>
@@ -4309,28 +4315,28 @@
         <v>61</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C65" s="5" t="s">
         <v>51</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>232</v>
+        <v>178</v>
       </c>
       <c r="F65" s="5" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="G65" s="5" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="H65" s="5" t="s">
-        <v>83</v>
+        <v>55</v>
       </c>
       <c r="I65" s="10" t="s">
-        <v>230</v>
+        <v>116</v>
       </c>
       <c r="J65" s="10" t="n">
         <v>2</v>
@@ -4340,7 +4346,7 @@
       </c>
       <c r="L65" s="10" t="str">
         <f aca="false">IF(OR(J65="",H65="(belum memilih)",H65="(organik)"),"",IF(OR(H65="7 &amp; 8 Okt",H65="(kosong)",AND(H65="7 Okt",J65=1),AND(H65="8 Okt",J65=2)),"Ya","Tidak"))</f>
-        <v>Ya</v>
+        <v>Tidak</v>
       </c>
       <c r="M65" s="5"/>
     </row>
@@ -4349,28 +4355,28 @@
         <v>62</v>
       </c>
       <c r="B66" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D66" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E66" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="F66" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="G66" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="H66" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="I66" s="10" t="s">
         <v>234</v>
-      </c>
-      <c r="C66" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="D66" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E66" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="F66" s="5" t="s">
-        <v>236</v>
-      </c>
-      <c r="G66" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="H66" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="I66" s="10" t="s">
-        <v>71</v>
       </c>
       <c r="J66" s="10" t="n">
         <v>2</v>
@@ -4380,7 +4386,7 @@
       </c>
       <c r="L66" s="10" t="str">
         <f aca="false">IF(OR(J66="",H66="(belum memilih)",H66="(organik)"),"",IF(OR(H66="7 &amp; 8 Okt",H66="(kosong)",AND(H66="7 Okt",J66=1),AND(H66="8 Okt",J66=2)),"Ya","Tidak"))</f>
-        <v>Tidak</v>
+        <v>Ya</v>
       </c>
       <c r="M66" s="5"/>
     </row>
@@ -4389,7 +4395,7 @@
         <v>63</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C67" s="5" t="s">
         <v>51</v>
@@ -4398,19 +4404,19 @@
         <v>24</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="G67" s="5" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="H67" s="5" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="I67" s="10" t="s">
-        <v>118</v>
+        <v>234</v>
       </c>
       <c r="J67" s="10" t="n">
         <v>2</v>
@@ -4429,25 +4435,25 @@
         <v>64</v>
       </c>
       <c r="B68" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D68" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E68" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="F68" s="5" t="s">
         <v>240</v>
       </c>
-      <c r="C68" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="D68" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E68" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="F68" s="5" t="s">
-        <v>241</v>
-      </c>
       <c r="G68" s="5" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="H68" s="5" t="s">
-        <v>91</v>
+        <v>55</v>
       </c>
       <c r="I68" s="10" t="s">
         <v>71</v>
@@ -4460,7 +4466,7 @@
       </c>
       <c r="L68" s="10" t="str">
         <f aca="false">IF(OR(J68="",H68="(belum memilih)",H68="(organik)"),"",IF(OR(H68="7 &amp; 8 Okt",H68="(kosong)",AND(H68="7 Okt",J68=1),AND(H68="8 Okt",J68=2)),"Ya","Tidak"))</f>
-        <v>Ya</v>
+        <v>Tidak</v>
       </c>
       <c r="M68" s="5"/>
     </row>
@@ -4469,28 +4475,28 @@
         <v>65</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="D69" s="5" t="s">
         <v>24</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>115</v>
+        <v>242</v>
       </c>
       <c r="F69" s="5" t="s">
         <v>243</v>
       </c>
       <c r="G69" s="5" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="H69" s="5" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="I69" s="10" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="J69" s="10" t="n">
         <v>2</v>
@@ -4509,28 +4515,28 @@
         <v>66</v>
       </c>
       <c r="B70" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="C70" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D70" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E70" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="F70" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="C70" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="D70" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E70" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="F70" s="5" t="s">
-        <v>246</v>
-      </c>
       <c r="G70" s="5" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="H70" s="5" t="s">
         <v>91</v>
       </c>
       <c r="I70" s="10" t="s">
-        <v>247</v>
+        <v>71</v>
       </c>
       <c r="J70" s="10" t="n">
         <v>2</v>
@@ -4549,28 +4555,28 @@
         <v>67</v>
       </c>
       <c r="B71" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="C71" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D71" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E71" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="F71" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="G71" s="5" t="s">
         <v>248</v>
-      </c>
-      <c r="C71" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="D71" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E71" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="F71" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="G71" s="5" t="s">
-        <v>244</v>
       </c>
       <c r="H71" s="5" t="s">
         <v>83</v>
       </c>
       <c r="I71" s="10" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="J71" s="10" t="n">
         <v>2</v>
@@ -4589,28 +4595,28 @@
         <v>68</v>
       </c>
       <c r="B72" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="C72" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D72" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E72" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="F72" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="C72" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="D72" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E72" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="F72" s="5" t="s">
-        <v>251</v>
-      </c>
       <c r="G72" s="5" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="H72" s="5" t="s">
         <v>91</v>
       </c>
       <c r="I72" s="10" t="s">
-        <v>71</v>
+        <v>251</v>
       </c>
       <c r="J72" s="10" t="n">
         <v>2</v>
@@ -4632,25 +4638,25 @@
         <v>252</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>204</v>
+        <v>51</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F73" s="5" t="s">
         <v>253</v>
       </c>
       <c r="G73" s="5" t="s">
-        <v>54</v>
+        <v>248</v>
       </c>
       <c r="H73" s="5" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="I73" s="10" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="J73" s="10" t="n">
         <v>2</v>
@@ -4660,49 +4666,49 @@
       </c>
       <c r="L73" s="10" t="str">
         <f aca="false">IF(OR(J73="",H73="(belum memilih)",H73="(organik)"),"",IF(OR(H73="7 &amp; 8 Okt",H73="(kosong)",AND(H73="7 Okt",J73=1),AND(H73="8 Okt",J73=2)),"Ya","Tidak"))</f>
-        <v/>
-      </c>
-      <c r="M73" s="5" t="s">
-        <v>254</v>
-      </c>
+        <v>Ya</v>
+      </c>
+      <c r="M73" s="5"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="10" t="n">
         <v>70</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>143</v>
+        <v>51</v>
       </c>
       <c r="D74" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E74" s="5"/>
-      <c r="F74" s="5"/>
+      <c r="E74" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="F74" s="5" t="s">
+        <v>255</v>
+      </c>
       <c r="G74" s="5" t="s">
-        <v>10</v>
+        <v>248</v>
       </c>
       <c r="H74" s="5" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="I74" s="10" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="J74" s="10" t="n">
         <v>2</v>
       </c>
       <c r="K74" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L74" s="10" t="str">
         <f aca="false">IF(OR(J74="",H74="(belum memilih)",H74="(organik)"),"",IF(OR(H74="7 &amp; 8 Okt",H74="(kosong)",AND(H74="7 Okt",J74=1),AND(H74="8 Okt",J74=2)),"Ya","Tidak"))</f>
-        <v/>
-      </c>
-      <c r="M74" s="5" t="s">
-        <v>144</v>
-      </c>
+        <v>Ya</v>
+      </c>
+      <c r="M74" s="5"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="10" t="n">
@@ -4712,34 +4718,38 @@
         <v>256</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>143</v>
+        <v>51</v>
       </c>
       <c r="D75" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E75" s="5"/>
-      <c r="F75" s="5"/>
+      <c r="E75" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="F75" s="5" t="s">
+        <v>257</v>
+      </c>
       <c r="G75" s="5" t="s">
-        <v>10</v>
+        <v>248</v>
       </c>
       <c r="H75" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I75" s="10" t="s">
-        <v>75</v>
+        <v>101</v>
       </c>
       <c r="J75" s="10" t="n">
         <v>2</v>
       </c>
       <c r="K75" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L75" s="10" t="str">
         <f aca="false">IF(OR(J75="",H75="(belum memilih)",H75="(organik)"),"",IF(OR(H75="7 &amp; 8 Okt",H75="(kosong)",AND(H75="7 Okt",J75=1),AND(H75="8 Okt",J75=2)),"Ya","Tidak"))</f>
         <v/>
       </c>
       <c r="M75" s="5" t="s">
-        <v>144</v>
+        <v>102</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4747,13 +4757,13 @@
         <v>72</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>204</v>
+        <v>24</v>
       </c>
       <c r="E76" s="5"/>
       <c r="F76" s="5"/>
@@ -4777,7 +4787,7 @@
         <v/>
       </c>
       <c r="M76" s="5" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4785,28 +4795,24 @@
         <v>73</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>51</v>
+        <v>145</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E77" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="F77" s="5" t="s">
-        <v>259</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="E77" s="5"/>
+      <c r="F77" s="5"/>
       <c r="G77" s="5" t="s">
-        <v>54</v>
+        <v>10</v>
       </c>
       <c r="H77" s="5" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="I77" s="10" t="s">
-        <v>160</v>
+        <v>75</v>
       </c>
       <c r="J77" s="10" t="n">
         <v>2</v>
@@ -4816,10 +4822,10 @@
       </c>
       <c r="L77" s="10" t="str">
         <f aca="false">IF(OR(J77="",H77="(belum memilih)",H77="(organik)"),"",IF(OR(H77="7 &amp; 8 Okt",H77="(kosong)",AND(H77="7 Okt",J77=1),AND(H77="8 Okt",J77=2)),"Ya","Tidak"))</f>
-        <v>Ya</v>
+        <v/>
       </c>
       <c r="M77" s="5" t="s">
-        <v>57</v>
+        <v>146</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4830,18 +4836,18 @@
         <v>260</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>63</v>
+        <v>145</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>21</v>
+        <v>208</v>
       </c>
       <c r="E78" s="5"/>
       <c r="F78" s="5"/>
       <c r="G78" s="5" t="s">
-        <v>261</v>
+        <v>10</v>
       </c>
       <c r="H78" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I78" s="10" t="s">
         <v>75</v>
@@ -4857,7 +4863,7 @@
         <v/>
       </c>
       <c r="M78" s="5" t="s">
-        <v>76</v>
+        <v>146</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4865,28 +4871,28 @@
         <v>75</v>
       </c>
       <c r="B79" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="C79" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D79" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E79" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F79" s="5" t="s">
         <v>262</v>
       </c>
-      <c r="C79" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="D79" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E79" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="F79" s="5" t="s">
-        <v>264</v>
-      </c>
       <c r="G79" s="5" t="s">
-        <v>261</v>
+        <v>54</v>
       </c>
       <c r="H79" s="5" t="s">
         <v>83</v>
       </c>
       <c r="I79" s="10" t="s">
-        <v>265</v>
+        <v>162</v>
       </c>
       <c r="J79" s="10" t="n">
         <v>2</v>
@@ -4898,35 +4904,33 @@
         <f aca="false">IF(OR(J79="",H79="(belum memilih)",H79="(organik)"),"",IF(OR(H79="7 &amp; 8 Okt",H79="(kosong)",AND(H79="7 Okt",J79=1),AND(H79="8 Okt",J79=2)),"Ya","Tidak"))</f>
         <v>Ya</v>
       </c>
-      <c r="M79" s="5"/>
+      <c r="M79" s="5" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="10" t="n">
         <v>76</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="D80" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E80" s="5" t="s">
-        <v>267</v>
-      </c>
-      <c r="F80" s="5" t="s">
-        <v>268</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="E80" s="5"/>
+      <c r="F80" s="5"/>
       <c r="G80" s="5" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="H80" s="5" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="I80" s="10" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="J80" s="10" t="n">
         <v>2</v>
@@ -4936,37 +4940,39 @@
       </c>
       <c r="L80" s="10" t="str">
         <f aca="false">IF(OR(J80="",H80="(belum memilih)",H80="(organik)"),"",IF(OR(H80="7 &amp; 8 Okt",H80="(kosong)",AND(H80="7 Okt",J80=1),AND(H80="8 Okt",J80=2)),"Ya","Tidak"))</f>
-        <v>Ya</v>
-      </c>
-      <c r="M80" s="5"/>
+        <v/>
+      </c>
+      <c r="M80" s="5" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="10" t="n">
         <v>77</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="C81" s="5" t="s">
         <v>51</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E81" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="F81" s="5" t="s">
         <v>267</v>
       </c>
-      <c r="F81" s="5" t="s">
-        <v>270</v>
-      </c>
       <c r="G81" s="5" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="H81" s="5" t="s">
         <v>83</v>
       </c>
       <c r="I81" s="10" t="s">
-        <v>71</v>
+        <v>268</v>
       </c>
       <c r="J81" s="10" t="n">
         <v>2</v>
@@ -4985,25 +4991,25 @@
         <v>78</v>
       </c>
       <c r="B82" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="C82" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D82" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E82" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="F82" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="C82" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="D82" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E82" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="F82" s="5" t="s">
-        <v>272</v>
-      </c>
       <c r="G82" s="5" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="H82" s="5" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="I82" s="10" t="s">
         <v>71</v>
@@ -5016,7 +5022,7 @@
       </c>
       <c r="L82" s="10" t="str">
         <f aca="false">IF(OR(J82="",H82="(belum memilih)",H82="(organik)"),"",IF(OR(H82="7 &amp; 8 Okt",H82="(kosong)",AND(H82="7 Okt",J82=1),AND(H82="8 Okt",J82=2)),"Ya","Tidak"))</f>
-        <v>Tidak</v>
+        <v>Ya</v>
       </c>
       <c r="M82" s="5"/>
     </row>
@@ -5025,28 +5031,28 @@
         <v>79</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C83" s="5" t="s">
         <v>51</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>78</v>
+        <v>270</v>
       </c>
       <c r="F83" s="5" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="G83" s="5" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="H83" s="5" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="I83" s="10" t="s">
-        <v>276</v>
+        <v>71</v>
       </c>
       <c r="J83" s="10" t="n">
         <v>2</v>
@@ -5056,7 +5062,7 @@
       </c>
       <c r="L83" s="10" t="str">
         <f aca="false">IF(OR(J83="",H83="(belum memilih)",H83="(organik)"),"",IF(OR(H83="7 &amp; 8 Okt",H83="(kosong)",AND(H83="7 Okt",J83=1),AND(H83="8 Okt",J83=2)),"Ya","Tidak"))</f>
-        <v>Tidak</v>
+        <v>Ya</v>
       </c>
       <c r="M83" s="5"/>
     </row>
@@ -5065,28 +5071,28 @@
         <v>80</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>210</v>
+        <v>81</v>
       </c>
       <c r="F84" s="5" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="G84" s="5" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="H84" s="5" t="s">
-        <v>91</v>
+        <v>55</v>
       </c>
       <c r="I84" s="10" t="s">
-        <v>160</v>
+        <v>71</v>
       </c>
       <c r="J84" s="10" t="n">
         <v>2</v>
@@ -5096,7 +5102,7 @@
       </c>
       <c r="L84" s="10" t="str">
         <f aca="false">IF(OR(J84="",H84="(belum memilih)",H84="(organik)"),"",IF(OR(H84="7 &amp; 8 Okt",H84="(kosong)",AND(H84="7 Okt",J84=1),AND(H84="8 Okt",J84=2)),"Ya","Tidak"))</f>
-        <v>Ya</v>
+        <v>Tidak</v>
       </c>
       <c r="M84" s="5"/>
     </row>
@@ -5105,28 +5111,28 @@
         <v>81</v>
       </c>
       <c r="B85" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="C85" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D85" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E85" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F85" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="G85" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="H85" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="I85" s="10" t="s">
         <v>279</v>
-      </c>
-      <c r="C85" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="D85" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E85" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="F85" s="5" t="s">
-        <v>280</v>
-      </c>
-      <c r="G85" s="5" t="s">
-        <v>273</v>
-      </c>
-      <c r="H85" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="I85" s="10" t="s">
-        <v>160</v>
       </c>
       <c r="J85" s="10" t="n">
         <v>2</v>
@@ -5136,7 +5142,7 @@
       </c>
       <c r="L85" s="10" t="str">
         <f aca="false">IF(OR(J85="",H85="(belum memilih)",H85="(organik)"),"",IF(OR(H85="7 &amp; 8 Okt",H85="(kosong)",AND(H85="7 Okt",J85=1),AND(H85="8 Okt",J85=2)),"Ya","Tidak"))</f>
-        <v>Ya</v>
+        <v>Tidak</v>
       </c>
       <c r="M85" s="5"/>
     </row>
@@ -5145,7 +5151,7 @@
         <v>82</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C86" s="5" t="s">
         <v>51</v>
@@ -5154,19 +5160,19 @@
         <v>29</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G86" s="5" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="H86" s="5" t="s">
         <v>91</v>
       </c>
       <c r="I86" s="10" t="s">
-        <v>103</v>
+        <v>162</v>
       </c>
       <c r="J86" s="10" t="n">
         <v>2</v>
@@ -5185,28 +5191,28 @@
         <v>83</v>
       </c>
       <c r="B87" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="C87" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D87" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E87" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="F87" s="5" t="s">
         <v>283</v>
       </c>
-      <c r="C87" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="D87" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E87" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="F87" s="5" t="s">
-        <v>284</v>
-      </c>
       <c r="G87" s="5" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="H87" s="5" t="s">
-        <v>55</v>
+        <v>91</v>
       </c>
       <c r="I87" s="10" t="s">
-        <v>276</v>
+        <v>162</v>
       </c>
       <c r="J87" s="10" t="n">
         <v>2</v>
@@ -5216,7 +5222,7 @@
       </c>
       <c r="L87" s="10" t="str">
         <f aca="false">IF(OR(J87="",H87="(belum memilih)",H87="(organik)"),"",IF(OR(H87="7 &amp; 8 Okt",H87="(kosong)",AND(H87="7 Okt",J87=1),AND(H87="8 Okt",J87=2)),"Ya","Tidak"))</f>
-        <v>Tidak</v>
+        <v>Ya</v>
       </c>
       <c r="M87" s="5"/>
     </row>
@@ -5225,28 +5231,28 @@
         <v>84</v>
       </c>
       <c r="B88" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="C88" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D88" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E88" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="F88" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="C88" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="D88" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E88" s="5" t="s">
-        <v>286</v>
-      </c>
-      <c r="F88" s="5" t="s">
-        <v>287</v>
-      </c>
       <c r="G88" s="5" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="H88" s="5" t="s">
         <v>91</v>
       </c>
       <c r="I88" s="10" t="s">
-        <v>67</v>
+        <v>106</v>
       </c>
       <c r="J88" s="10" t="n">
         <v>2</v>
@@ -5265,28 +5271,28 @@
         <v>85</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C89" s="5" t="s">
         <v>51</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>232</v>
+        <v>78</v>
       </c>
       <c r="F89" s="5" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="G89" s="5" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="H89" s="5" t="s">
-        <v>83</v>
+        <v>55</v>
       </c>
       <c r="I89" s="10" t="s">
-        <v>71</v>
+        <v>279</v>
       </c>
       <c r="J89" s="10" t="n">
         <v>2</v>
@@ -5296,7 +5302,7 @@
       </c>
       <c r="L89" s="10" t="str">
         <f aca="false">IF(OR(J89="",H89="(belum memilih)",H89="(organik)"),"",IF(OR(H89="7 &amp; 8 Okt",H89="(kosong)",AND(H89="7 Okt",J89=1),AND(H89="8 Okt",J89=2)),"Ya","Tidak"))</f>
-        <v>Ya</v>
+        <v>Tidak</v>
       </c>
       <c r="M89" s="5"/>
     </row>
@@ -5305,7 +5311,7 @@
         <v>86</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="C90" s="5" t="s">
         <v>63</v>
@@ -5314,19 +5320,19 @@
         <v>24</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>169</v>
+        <v>289</v>
       </c>
       <c r="F90" s="5" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="G90" s="5" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="H90" s="5" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="I90" s="10" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="J90" s="10" t="n">
         <v>2</v>
@@ -5345,7 +5351,7 @@
         <v>87</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C91" s="5" t="s">
         <v>51</v>
@@ -5354,16 +5360,16 @@
         <v>24</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>69</v>
+        <v>236</v>
       </c>
       <c r="F91" s="5" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="G91" s="5" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="H91" s="5" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="I91" s="10" t="s">
         <v>71</v>
@@ -5376,7 +5382,7 @@
       </c>
       <c r="L91" s="10" t="str">
         <f aca="false">IF(OR(J91="",H91="(belum memilih)",H91="(organik)"),"",IF(OR(H91="7 &amp; 8 Okt",H91="(kosong)",AND(H91="7 Okt",J91=1),AND(H91="8 Okt",J91=2)),"Ya","Tidak"))</f>
-        <v>Tidak</v>
+        <v>Ya</v>
       </c>
       <c r="M91" s="5"/>
     </row>
@@ -5385,28 +5391,28 @@
         <v>88</v>
       </c>
       <c r="B92" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="C92" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D92" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E92" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="F92" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="G92" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="C92" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="D92" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E92" s="5" t="s">
-        <v>297</v>
-      </c>
-      <c r="F92" s="5" t="s">
-        <v>298</v>
-      </c>
-      <c r="G92" s="5" t="s">
-        <v>293</v>
-      </c>
       <c r="H92" s="5" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="I92" s="10" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="J92" s="10" t="n">
         <v>2</v>
@@ -5425,28 +5431,28 @@
         <v>89</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C93" s="5" t="s">
         <v>51</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>107</v>
+        <v>69</v>
       </c>
       <c r="F93" s="5" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="G93" s="5" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="H93" s="5" t="s">
-        <v>91</v>
+        <v>55</v>
       </c>
       <c r="I93" s="10" t="s">
-        <v>113</v>
+        <v>71</v>
       </c>
       <c r="J93" s="10" t="n">
         <v>2</v>
@@ -5456,7 +5462,7 @@
       </c>
       <c r="L93" s="10" t="str">
         <f aca="false">IF(OR(J93="",H93="(belum memilih)",H93="(organik)"),"",IF(OR(H93="7 &amp; 8 Okt",H93="(kosong)",AND(H93="7 Okt",J93=1),AND(H93="8 Okt",J93=2)),"Ya","Tidak"))</f>
-        <v>Ya</v>
+        <v>Tidak</v>
       </c>
       <c r="M93" s="5"/>
     </row>
@@ -5465,7 +5471,7 @@
         <v>90</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C94" s="5" t="s">
         <v>51</v>
@@ -5474,13 +5480,13 @@
         <v>21</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="F94" s="5" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="G94" s="5" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="H94" s="5" t="s">
         <v>91</v>
@@ -5500,29 +5506,33 @@
       </c>
       <c r="M94" s="5"/>
     </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="10" t="n">
         <v>91</v>
       </c>
       <c r="B95" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="C95" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D95" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E95" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="F95" s="5" t="s">
         <v>303</v>
       </c>
-      <c r="C95" s="5" t="s">
-        <v>204</v>
-      </c>
-      <c r="D95" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E95" s="5"/>
-      <c r="F95" s="5"/>
       <c r="G95" s="5" t="s">
-        <v>54</v>
+        <v>296</v>
       </c>
       <c r="H95" s="5" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="I95" s="10" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="J95" s="10" t="n">
         <v>2</v>
@@ -5532,13 +5542,11 @@
       </c>
       <c r="L95" s="10" t="str">
         <f aca="false">IF(OR(J95="",H95="(belum memilih)",H95="(organik)"),"",IF(OR(H95="7 &amp; 8 Okt",H95="(kosong)",AND(H95="7 Okt",J95=1),AND(H95="8 Okt",J95=2)),"Ya","Tidak"))</f>
-        <v/>
-      </c>
-      <c r="M95" s="5" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>Ya</v>
+      </c>
+      <c r="M95" s="5"/>
+    </row>
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="10" t="n">
         <v>92</v>
       </c>
@@ -5546,38 +5554,78 @@
         <v>304</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>204</v>
+        <v>51</v>
       </c>
       <c r="D96" s="5" t="s">
         <v>21</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>107</v>
+        <v>300</v>
       </c>
       <c r="F96" s="5" t="s">
         <v>305</v>
       </c>
       <c r="G96" s="5" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="H96" s="5" t="s">
         <v>91</v>
       </c>
       <c r="I96" s="10" t="s">
-        <v>230</v>
-      </c>
-      <c r="J96" s="10"/>
-      <c r="K96" s="10"/>
+        <v>67</v>
+      </c>
+      <c r="J96" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K96" s="10" t="n">
+        <v>4</v>
+      </c>
       <c r="L96" s="10" t="str">
+        <f aca="false">IF(OR(J96="",H96="(belum memilih)",H96="(organik)"),"",IF(OR(H96="7 &amp; 8 Okt",H96="(kosong)",AND(H96="7 Okt",J96=1),AND(H96="8 Okt",J96=2)),"Ya","Tidak"))</f>
+        <v>Ya</v>
+      </c>
+      <c r="M96" s="5"/>
+    </row>
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="10" t="n">
+        <v>93</v>
+      </c>
+      <c r="B97" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="C97" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="D97" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E97" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="F97" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="G97" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="H97" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="I97" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="J97" s="10"/>
+      <c r="K97" s="10"/>
+      <c r="L97" s="10" t="str">
         <f aca="false">IF(OR(J92="",H92="(belum memilih)",H92="(organik)"),"",IF(OR(H92="7 &amp; 8 Okt",H92="(kosong)",AND(H92="7 Okt",J92=1),AND(H92="8 Okt",J92=2)),"Ya","Tidak"))</f>
         <v>Ya</v>
       </c>
-      <c r="M96" s="5" t="s">
-        <v>307</v>
+      <c r="M97" s="5" t="s">
+        <v>309</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:M96"/>
+  <autoFilter ref="A4:M97"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -5609,7 +5657,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5620,25 +5668,25 @@
         <v>46</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5649,29 +5697,29 @@
         <v>1</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="D4" s="11" t="n">
-        <f aca="false">COUNTIFS('Daftar Peserta'!$K$5:$K$96,1,'Daftar Peserta'!$C$5:$C$96,"&lt;&gt;SIT-IN")</f>
-        <v>25</v>
+        <f aca="false">COUNTIFS('Daftar Peserta'!$K$5:$K$97,1,'Daftar Peserta'!$C$5:$C$97,"&lt;&gt;SIT-IN")</f>
+        <v>26</v>
       </c>
       <c r="E4" s="11" t="n">
-        <f aca="false">COUNTIFS('Daftar Peserta'!$K$5:$K$96,1,'Daftar Peserta'!$C$5:$C$96,"SIT-IN")</f>
+        <f aca="false">COUNTIFS('Daftar Peserta'!$K$5:$K$97,1,'Daftar Peserta'!$C$5:$C$97,"SIT-IN")</f>
         <v>0</v>
       </c>
       <c r="F4" s="11" t="n">
         <f aca="false">D4+E4</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G4" s="11" t="str">
         <f aca="false">IF(AND(F4&gt;=20,F4&lt;=27),"OK",IF(F4&lt;20,"Kurang "&amp;(20-F4),"Lebih "&amp;(F4-27)))</f>
         <v>OK</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5682,29 +5730,29 @@
         <v>2</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="D5" s="11" t="n">
-        <f aca="false">COUNTIFS('Daftar Peserta'!$K$5:$K$96,2,'Daftar Peserta'!$C$5:$C$96,"&lt;&gt;SIT-IN")</f>
-        <v>20</v>
+        <f aca="false">COUNTIFS('Daftar Peserta'!$K$5:$K$97,2,'Daftar Peserta'!$C$5:$C$97,"&lt;&gt;SIT-IN")</f>
+        <v>21</v>
       </c>
       <c r="E5" s="11" t="n">
-        <f aca="false">COUNTIFS('Daftar Peserta'!$K$5:$K$96,2,'Daftar Peserta'!$C$5:$C$96,"SIT-IN")</f>
+        <f aca="false">COUNTIFS('Daftar Peserta'!$K$5:$K$97,2,'Daftar Peserta'!$C$5:$C$97,"SIT-IN")</f>
         <v>2</v>
       </c>
       <c r="F5" s="11" t="n">
         <f aca="false">D5+E5</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G5" s="11" t="str">
         <f aca="false">IF(AND(F5&gt;=20,F5&lt;=27),"OK",IF(F5&lt;20,"Kurang "&amp;(20-F5),"Lebih "&amp;(F5-27)))</f>
         <v>OK</v>
       </c>
       <c r="H5" s="12" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="I5" s="12" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5715,14 +5763,14 @@
         <v>2</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="D6" s="11" t="n">
-        <f aca="false">COUNTIFS('Daftar Peserta'!$K$5:$K$96,3,'Daftar Peserta'!$C$5:$C$96,"&lt;&gt;SIT-IN")</f>
+        <f aca="false">COUNTIFS('Daftar Peserta'!$K$5:$K$97,3,'Daftar Peserta'!$C$5:$C$97,"&lt;&gt;SIT-IN")</f>
         <v>19</v>
       </c>
       <c r="E6" s="11" t="n">
-        <f aca="false">COUNTIFS('Daftar Peserta'!$K$5:$K$96,3,'Daftar Peserta'!$C$5:$C$96,"SIT-IN")</f>
+        <f aca="false">COUNTIFS('Daftar Peserta'!$K$5:$K$97,3,'Daftar Peserta'!$C$5:$C$97,"SIT-IN")</f>
         <v>3</v>
       </c>
       <c r="F6" s="11" t="n">
@@ -5734,10 +5782,10 @@
         <v>OK</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="I6" s="12" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5748,38 +5796,38 @@
         <v>2</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="D7" s="11" t="n">
-        <f aca="false">COUNTIFS('Daftar Peserta'!$K$5:$K$96,4,'Daftar Peserta'!$C$5:$C$96,"&lt;&gt;SIT-IN")</f>
-        <v>19</v>
+        <f aca="false">COUNTIFS('Daftar Peserta'!$K$5:$K$97,4,'Daftar Peserta'!$C$5:$C$97,"&lt;&gt;SIT-IN")</f>
+        <v>18</v>
       </c>
       <c r="E7" s="11" t="n">
-        <f aca="false">COUNTIFS('Daftar Peserta'!$K$5:$K$96,4,'Daftar Peserta'!$C$5:$C$96,"SIT-IN")</f>
+        <f aca="false">COUNTIFS('Daftar Peserta'!$K$5:$K$97,4,'Daftar Peserta'!$C$5:$C$97,"SIT-IN")</f>
         <v>3</v>
       </c>
       <c r="F7" s="11" t="n">
         <f aca="false">D7+E7</f>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G7" s="11" t="str">
         <f aca="false">IF(AND(F7&gt;=20,F7&lt;=27),"OK",IF(F7&lt;20,"Kurang "&amp;(20-F7),"Lebih "&amp;(F7-27)))</f>
         <v>OK</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="D8" s="14" t="n">
         <f aca="false">SUM(D4:D7)</f>
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E8" s="14" t="n">
         <f aca="false">SUM(E4:E7)</f>
@@ -5787,12 +5835,12 @@
       </c>
       <c r="F8" s="14" t="n">
         <f aca="false">SUM(F4:F7)</f>
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
   </sheetData>
@@ -5831,231 +5879,231 @@
         <v>47</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C2" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C3" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C4" s="5" t="n">
         <v>2</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C5" s="5" t="n">
         <v>2</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C6" s="5" t="n">
         <v>3</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C7" s="5" t="n">
         <v>3</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>4</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C9" s="5" t="n">
         <v>4</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C10" s="5" t="n">
         <v>2</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C11" s="5" t="n">
         <v>2</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="C12" s="5" t="n">
         <v>3</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="C13" s="5" t="n">
         <v>3</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="C14" s="5" t="n">
         <v>3</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="C15" s="5" t="n">
         <v>4</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C16" s="5" t="n">
         <v>4</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C17" s="5" t="n">
         <v>4</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
   </sheetData>
@@ -6093,16 +6141,16 @@
         <v>39</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>44</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6182,18 +6230,18 @@
         <v>1</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="15" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B6" s="15" t="s">
         <v>51</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D6" s="15" t="s">
         <v>91</v>
@@ -6202,18 +6250,18 @@
         <v>1</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="15" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B7" s="15" t="s">
         <v>51</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D7" s="15" t="s">
         <v>91</v>
@@ -6222,18 +6270,18 @@
         <v>1</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="15" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B8" s="15" t="s">
         <v>63</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D8" s="15" t="s">
         <v>91</v>
@@ -6242,18 +6290,18 @@
         <v>1</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B9" s="15" t="s">
         <v>63</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D9" s="15" t="s">
         <v>55</v>
@@ -6262,18 +6310,18 @@
         <v>2</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B10" s="15" t="s">
         <v>51</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D10" s="15" t="s">
         <v>55</v>
@@ -6282,18 +6330,18 @@
         <v>2</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="15" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B11" s="15" t="s">
         <v>51</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D11" s="15" t="s">
         <v>55</v>
@@ -6302,18 +6350,18 @@
         <v>2</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="15" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B12" s="15" t="s">
         <v>51</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="D12" s="15" t="s">
         <v>55</v>
@@ -6322,18 +6370,18 @@
         <v>2</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="B13" s="15" t="s">
         <v>51</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="D13" s="15" t="s">
         <v>55</v>
@@ -6342,18 +6390,18 @@
         <v>2</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="15" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B14" s="15" t="s">
         <v>51</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D14" s="15" t="s">
         <v>55</v>
@@ -6362,18 +6410,18 @@
         <v>2</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="15" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B15" s="15" t="s">
         <v>51</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D15" s="15" t="s">
         <v>55</v>
@@ -6382,18 +6430,18 @@
         <v>2</v>
       </c>
       <c r="F15" s="15" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="15" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="B16" s="15" t="s">
         <v>51</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="D16" s="15" t="s">
         <v>55</v>
@@ -6402,12 +6450,12 @@
         <v>2</v>
       </c>
       <c r="F16" s="15" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="B17" s="15" t="s">
         <v>51</v>
@@ -6427,13 +6475,13 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="15" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="B18" s="15" t="s">
         <v>63</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="D18" s="15" t="s">
         <v>55</v>
@@ -6442,18 +6490,18 @@
         <v>2</v>
       </c>
       <c r="F18" s="15" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="15" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="B19" s="15" t="s">
         <v>51</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="D19" s="15" t="s">
         <v>55</v>
@@ -6462,18 +6510,18 @@
         <v>2</v>
       </c>
       <c r="F19" s="15" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="15" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="B20" s="15" t="s">
         <v>51</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="D20" s="15" t="s">
         <v>55</v>
@@ -6482,18 +6530,18 @@
         <v>2</v>
       </c>
       <c r="F20" s="15" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="15" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="B21" s="15" t="s">
         <v>51</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D21" s="15" t="s">
         <v>55</v>
@@ -6502,27 +6550,27 @@
         <v>2</v>
       </c>
       <c r="F21" s="15" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="15" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D22" s="15" t="s">
         <v>91</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="F22" s="15" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
   </sheetData>
